--- a/research/traditional_assets/database/data/mauritius/mauritius_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_metals_mining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1172996728247131</v>
+        <v>0.117161973315476</v>
       </c>
       <c r="C2">
-        <v>1032.36739831004</v>
+        <v>1023.258074597978</v>
       </c>
       <c r="D2">
-        <v>962.5673983100403</v>
+        <v>963.7250745979782</v>
       </c>
       <c r="E2">
-        <v>-77.59999999999999</v>
+        <v>-67.333</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.267</v>
       </c>
       <c r="G2">
         <v>69.8</v>
@@ -1445,28 +1445,28 @@
         <v>213.031</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5164301</v>
       </c>
       <c r="N2">
-        <v>213.031</v>
+        <v>212.5145699</v>
       </c>
       <c r="O2">
-        <v>31.95465</v>
+        <v>31.877185485</v>
       </c>
       <c r="P2">
-        <v>181.07635</v>
+        <v>180.637384415</v>
       </c>
       <c r="Q2">
-        <v>181.54535</v>
+        <v>181.106384415</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1172996728247131</v>
+        <v>0.1179135589045212</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652958</v>
+        <v>0.9926702822236341</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>412.5069394677034</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.117161973315476</v>
+        <v>0.1170242738062389</v>
       </c>
       <c r="C3">
-        <v>1023.258074597978</v>
+        <v>1014.151538905128</v>
       </c>
       <c r="D3">
-        <v>963.7250745979782</v>
+        <v>964.8855389051278</v>
       </c>
       <c r="E3">
-        <v>-67.333</v>
+        <v>-57.06599999999999</v>
       </c>
       <c r="F3">
-        <v>10.267</v>
+        <v>20.534</v>
       </c>
       <c r="G3">
         <v>69.8</v>
@@ -1527,28 +1527,28 @@
         <v>213.031</v>
       </c>
       <c r="M3">
-        <v>0.5164301</v>
+        <v>1.0328602</v>
       </c>
       <c r="N3">
-        <v>212.5145699</v>
+        <v>211.9981398</v>
       </c>
       <c r="O3">
-        <v>31.877185485</v>
+        <v>31.79972097</v>
       </c>
       <c r="P3">
-        <v>180.637384415</v>
+        <v>180.19841883</v>
       </c>
       <c r="Q3">
-        <v>181.106384415</v>
+        <v>180.66741883</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1179135589045212</v>
+        <v>0.1185399732716724</v>
       </c>
       <c r="T3">
-        <v>0.9926702822236341</v>
+        <v>1.001293111772959</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>412.5069394677034</v>
+        <v>206.2534697338517</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1170242738062389</v>
+        <v>0.1168865742970018</v>
       </c>
       <c r="C4">
-        <v>1014.151538905128</v>
+        <v>1005.047801315165</v>
       </c>
       <c r="D4">
-        <v>964.8855389051278</v>
+        <v>966.0488013151655</v>
       </c>
       <c r="E4">
-        <v>-57.06599999999999</v>
+        <v>-46.79899999999999</v>
       </c>
       <c r="F4">
-        <v>20.534</v>
+        <v>30.801</v>
       </c>
       <c r="G4">
         <v>69.8</v>
@@ -1609,28 +1609,28 @@
         <v>213.031</v>
       </c>
       <c r="M4">
-        <v>1.0328602</v>
+        <v>1.5492903</v>
       </c>
       <c r="N4">
-        <v>211.9981398</v>
+        <v>211.4817097</v>
       </c>
       <c r="O4">
-        <v>31.79972097</v>
+        <v>31.722256455</v>
       </c>
       <c r="P4">
-        <v>180.19841883</v>
+        <v>179.759453245</v>
       </c>
       <c r="Q4">
-        <v>180.66741883</v>
+        <v>180.228453245</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1185399732716724</v>
+        <v>0.119179303398971</v>
       </c>
       <c r="T4">
-        <v>1.001293111772959</v>
+        <v>1.01009373162227</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>206.2534697338517</v>
+        <v>137.5023131559011</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1168865742970018</v>
+        <v>0.1167488747877648</v>
       </c>
       <c r="C5">
-        <v>1005.047801315165</v>
+        <v>995.9468719604547</v>
       </c>
       <c r="D5">
-        <v>966.0488013151655</v>
+        <v>967.2148719604547</v>
       </c>
       <c r="E5">
-        <v>-46.79899999999999</v>
+        <v>-36.53199999999999</v>
       </c>
       <c r="F5">
-        <v>30.801</v>
+        <v>41.068</v>
       </c>
       <c r="G5">
         <v>69.8</v>
@@ -1691,28 +1691,28 @@
         <v>213.031</v>
       </c>
       <c r="M5">
-        <v>1.5492903</v>
+        <v>2.0657204</v>
       </c>
       <c r="N5">
-        <v>211.4817097</v>
+        <v>210.9652796</v>
       </c>
       <c r="O5">
-        <v>31.722256455</v>
+        <v>31.64479194</v>
       </c>
       <c r="P5">
-        <v>179.759453245</v>
+        <v>179.32048766</v>
       </c>
       <c r="Q5">
-        <v>180.228453245</v>
+        <v>179.78948766</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.119179303398971</v>
+        <v>0.1198319529039217</v>
       </c>
       <c r="T5">
-        <v>1.01009373162227</v>
+        <v>1.019077697718442</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>137.5023131559011</v>
+        <v>103.1267348669258</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1167488747877648</v>
+        <v>0.1166111752785277</v>
       </c>
       <c r="C6">
-        <v>995.9468719604547</v>
+        <v>986.8487610223381</v>
       </c>
       <c r="D6">
-        <v>967.2148719604547</v>
+        <v>968.3837610223381</v>
       </c>
       <c r="E6">
-        <v>-36.53199999999999</v>
+        <v>-26.26499999999999</v>
       </c>
       <c r="F6">
-        <v>41.068</v>
+        <v>51.33500000000001</v>
       </c>
       <c r="G6">
         <v>69.8</v>
@@ -1773,28 +1773,28 @@
         <v>213.031</v>
       </c>
       <c r="M6">
-        <v>2.0657204</v>
+        <v>2.5821505</v>
       </c>
       <c r="N6">
-        <v>210.9652796</v>
+        <v>210.4488495</v>
       </c>
       <c r="O6">
-        <v>31.64479194</v>
+        <v>31.567327425</v>
       </c>
       <c r="P6">
-        <v>179.32048766</v>
+        <v>178.881522075</v>
       </c>
       <c r="Q6">
-        <v>179.78948766</v>
+        <v>179.350522075</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1198319529039217</v>
+        <v>0.1204983423984502</v>
       </c>
       <c r="T6">
-        <v>1.019077697718442</v>
+        <v>1.028250799942954</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>103.1267348669258</v>
+        <v>82.50138789354065</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1166111752785277</v>
+        <v>0.1164734757692906</v>
       </c>
       <c r="C7">
-        <v>986.8487610223381</v>
+        <v>977.7534787314352</v>
       </c>
       <c r="D7">
-        <v>968.3837610223381</v>
+        <v>969.5554787314352</v>
       </c>
       <c r="E7">
-        <v>-26.26499999999999</v>
+        <v>-15.99799999999998</v>
       </c>
       <c r="F7">
-        <v>51.33500000000001</v>
+        <v>61.60200000000001</v>
       </c>
       <c r="G7">
         <v>69.8</v>
@@ -1855,28 +1855,28 @@
         <v>213.031</v>
       </c>
       <c r="M7">
-        <v>2.5821505</v>
+        <v>3.0985806</v>
       </c>
       <c r="N7">
-        <v>210.4488495</v>
+        <v>209.9324194</v>
       </c>
       <c r="O7">
-        <v>31.567327425</v>
+        <v>31.48986291</v>
       </c>
       <c r="P7">
-        <v>178.881522075</v>
+        <v>178.44255649</v>
       </c>
       <c r="Q7">
-        <v>179.350522075</v>
+        <v>178.91155649</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1204983423984502</v>
+        <v>0.1211789103928624</v>
       </c>
       <c r="T7">
-        <v>1.028250799942954</v>
+        <v>1.037619074555221</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>82.50138789354065</v>
+        <v>68.75115657795055</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1164734757692906</v>
+        <v>0.1163357762600536</v>
       </c>
       <c r="C8">
-        <v>977.7534787314354</v>
+        <v>968.6610353679404</v>
       </c>
       <c r="D8">
-        <v>969.5554787314353</v>
+        <v>970.7300353679404</v>
       </c>
       <c r="E8">
-        <v>-15.99799999999999</v>
+        <v>-5.730999999999995</v>
       </c>
       <c r="F8">
-        <v>61.602</v>
+        <v>71.869</v>
       </c>
       <c r="G8">
         <v>69.8</v>
@@ -1937,28 +1937,28 @@
         <v>213.031</v>
       </c>
       <c r="M8">
-        <v>3.0985806</v>
+        <v>3.6150107</v>
       </c>
       <c r="N8">
-        <v>209.9324194</v>
+        <v>209.4159893</v>
       </c>
       <c r="O8">
-        <v>31.48986291</v>
+        <v>31.412398395</v>
       </c>
       <c r="P8">
-        <v>178.44255649</v>
+        <v>178.003590905</v>
       </c>
       <c r="Q8">
-        <v>178.91155649</v>
+        <v>178.472590905</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1211789103928624</v>
+        <v>0.1218741142581221</v>
       </c>
       <c r="T8">
-        <v>1.037619074555221</v>
+        <v>1.047188817438721</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>68.75115657795057</v>
+        <v>58.92956278110049</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1163357762600536</v>
+        <v>0.1161980767508165</v>
       </c>
       <c r="C9">
-        <v>968.6610353679406</v>
+        <v>959.5714412619257</v>
       </c>
       <c r="D9">
-        <v>970.7300353679407</v>
+        <v>971.9074412619256</v>
       </c>
       <c r="E9">
-        <v>-5.73099999999998</v>
+        <v>4.536000000000016</v>
       </c>
       <c r="F9">
-        <v>71.86900000000001</v>
+        <v>82.13600000000001</v>
       </c>
       <c r="G9">
         <v>69.8</v>
@@ -2019,28 +2019,28 @@
         <v>213.031</v>
       </c>
       <c r="M9">
-        <v>3.6150107</v>
+        <v>4.1314408</v>
       </c>
       <c r="N9">
-        <v>209.4159893</v>
+        <v>208.8995592</v>
       </c>
       <c r="O9">
-        <v>31.412398395</v>
+        <v>31.33493388</v>
       </c>
       <c r="P9">
-        <v>178.003590905</v>
+        <v>177.56462532</v>
       </c>
       <c r="Q9">
-        <v>178.472590905</v>
+        <v>178.03362532</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1218741142581221</v>
+        <v>0.1225844312508875</v>
       </c>
       <c r="T9">
-        <v>1.047188817438721</v>
+        <v>1.056966598210991</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>58.92956278110048</v>
+        <v>51.56336743346292</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1161980767508165</v>
+        <v>0.1160603772415794</v>
       </c>
       <c r="C10">
-        <v>959.5714412619257</v>
+        <v>950.484706793638</v>
       </c>
       <c r="D10">
-        <v>971.9074412619256</v>
+        <v>973.0877067936379</v>
       </c>
       <c r="E10">
-        <v>4.536000000000016</v>
+        <v>14.80300000000001</v>
       </c>
       <c r="F10">
-        <v>82.13600000000001</v>
+        <v>92.40300000000001</v>
       </c>
       <c r="G10">
         <v>69.8</v>
@@ -2101,28 +2101,28 @@
         <v>213.031</v>
       </c>
       <c r="M10">
-        <v>4.1314408</v>
+        <v>4.6478709</v>
       </c>
       <c r="N10">
-        <v>208.8995592</v>
+        <v>208.3831291</v>
       </c>
       <c r="O10">
-        <v>31.33493388</v>
+        <v>31.257469365</v>
       </c>
       <c r="P10">
-        <v>177.56462532</v>
+        <v>177.125659735</v>
       </c>
       <c r="Q10">
-        <v>178.03362532</v>
+        <v>177.594659735</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1225844312508875</v>
+        <v>0.1233103596061312</v>
       </c>
       <c r="T10">
-        <v>1.056966598210991</v>
+        <v>1.066959275263972</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>51.56336743346292</v>
+        <v>45.83410438530038</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1160603772415794</v>
+        <v>0.1159226777323424</v>
       </c>
       <c r="C11">
-        <v>950.484706793638</v>
+        <v>941.4008423938106</v>
       </c>
       <c r="D11">
-        <v>973.0877067936379</v>
+        <v>974.2708423938107</v>
       </c>
       <c r="E11">
-        <v>14.80300000000001</v>
+        <v>25.07000000000001</v>
       </c>
       <c r="F11">
-        <v>92.40300000000001</v>
+        <v>102.67</v>
       </c>
       <c r="G11">
         <v>69.8</v>
@@ -2183,28 +2183,28 @@
         <v>213.031</v>
       </c>
       <c r="M11">
-        <v>4.6478709</v>
+        <v>5.164301</v>
       </c>
       <c r="N11">
-        <v>208.3831291</v>
+        <v>207.866699</v>
       </c>
       <c r="O11">
-        <v>31.257469365</v>
+        <v>31.18000485</v>
       </c>
       <c r="P11">
-        <v>177.125659735</v>
+        <v>176.68669415</v>
       </c>
       <c r="Q11">
-        <v>177.594659735</v>
+        <v>177.15569415</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1233103596061312</v>
+        <v>0.1240524197026026</v>
       </c>
       <c r="T11">
-        <v>1.066959275263972</v>
+        <v>1.077174011807018</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>45.83410438530038</v>
+        <v>41.25069394677034</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1159226777323424</v>
+        <v>0.1157849782231053</v>
       </c>
       <c r="C12">
-        <v>941.4008423938105</v>
+        <v>932.3198585439674</v>
       </c>
       <c r="D12">
-        <v>974.2708423938107</v>
+        <v>975.4568585439673</v>
       </c>
       <c r="E12">
-        <v>25.07000000000002</v>
+        <v>35.33700000000002</v>
       </c>
       <c r="F12">
-        <v>102.67</v>
+        <v>112.937</v>
       </c>
       <c r="G12">
         <v>69.8</v>
@@ -2265,28 +2265,28 @@
         <v>213.031</v>
       </c>
       <c r="M12">
-        <v>5.164301000000001</v>
+        <v>5.6807311</v>
       </c>
       <c r="N12">
-        <v>207.866699</v>
+        <v>207.3502689</v>
       </c>
       <c r="O12">
-        <v>31.18000485</v>
+        <v>31.102540335</v>
       </c>
       <c r="P12">
-        <v>176.68669415</v>
+        <v>176.247728565</v>
       </c>
       <c r="Q12">
-        <v>177.15569415</v>
+        <v>176.716728565</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1240524197026026</v>
+        <v>0.1248111553068599</v>
       </c>
       <c r="T12">
-        <v>1.077174011807018</v>
+        <v>1.087618292991481</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>41.25069394677033</v>
+        <v>37.5006308607003</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1157849782231053</v>
+        <v>0.1156472787138682</v>
       </c>
       <c r="C13">
-        <v>932.3198585439674</v>
+        <v>923.2417657767317</v>
       </c>
       <c r="D13">
-        <v>975.4568585439673</v>
+        <v>976.6457657767315</v>
       </c>
       <c r="E13">
-        <v>35.33700000000002</v>
+        <v>45.60400000000001</v>
       </c>
       <c r="F13">
-        <v>112.937</v>
+        <v>123.204</v>
       </c>
       <c r="G13">
         <v>69.8</v>
@@ -2347,28 +2347,28 @@
         <v>213.031</v>
       </c>
       <c r="M13">
-        <v>5.6807311</v>
+        <v>6.1971612</v>
       </c>
       <c r="N13">
-        <v>207.3502689</v>
+        <v>206.8338388</v>
       </c>
       <c r="O13">
-        <v>31.102540335</v>
+        <v>31.02507582</v>
       </c>
       <c r="P13">
-        <v>176.247728565</v>
+        <v>175.80876298</v>
       </c>
       <c r="Q13">
-        <v>176.716728565</v>
+        <v>176.27776298</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1248111553068599</v>
+        <v>0.125587134902123</v>
       </c>
       <c r="T13">
-        <v>1.087618292991481</v>
+        <v>1.098299944202864</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>37.5006308607003</v>
+        <v>34.37557828897528</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1156472787138682</v>
+        <v>0.1155095792046312</v>
       </c>
       <c r="C14">
-        <v>923.2417657767317</v>
+        <v>914.1665746761394</v>
       </c>
       <c r="D14">
-        <v>976.6457657767315</v>
+        <v>977.8375746761394</v>
       </c>
       <c r="E14">
-        <v>45.60400000000001</v>
+        <v>55.87100000000001</v>
       </c>
       <c r="F14">
-        <v>123.204</v>
+        <v>133.471</v>
       </c>
       <c r="G14">
         <v>69.8</v>
@@ -2429,28 +2429,28 @@
         <v>213.031</v>
       </c>
       <c r="M14">
-        <v>6.1971612</v>
+        <v>6.7135913</v>
       </c>
       <c r="N14">
-        <v>206.8338388</v>
+        <v>206.3174087</v>
       </c>
       <c r="O14">
-        <v>31.02507582</v>
+        <v>30.947611305</v>
       </c>
       <c r="P14">
-        <v>175.80876298</v>
+        <v>175.369797395</v>
       </c>
       <c r="Q14">
-        <v>176.27776298</v>
+        <v>175.838797395</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.125587134902123</v>
+        <v>0.1263809531087715</v>
       </c>
       <c r="T14">
-        <v>1.098299944202864</v>
+        <v>1.109227150614509</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>34.37557828897528</v>
+        <v>31.73130303597718</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1155095792046312</v>
+        <v>0.1153718796953941</v>
       </c>
       <c r="C15">
-        <v>914.1665746761394</v>
+        <v>905.0942958779533</v>
       </c>
       <c r="D15">
-        <v>977.8375746761394</v>
+        <v>979.0322958779533</v>
       </c>
       <c r="E15">
-        <v>55.87100000000001</v>
+        <v>66.13800000000003</v>
       </c>
       <c r="F15">
-        <v>133.471</v>
+        <v>143.738</v>
       </c>
       <c r="G15">
         <v>69.8</v>
@@ -2511,28 +2511,28 @@
         <v>213.031</v>
       </c>
       <c r="M15">
-        <v>6.7135913</v>
+        <v>7.230021400000001</v>
       </c>
       <c r="N15">
-        <v>206.3174087</v>
+        <v>205.8009786</v>
       </c>
       <c r="O15">
-        <v>30.947611305</v>
+        <v>30.87014679</v>
       </c>
       <c r="P15">
-        <v>175.369797395</v>
+        <v>174.93083181</v>
       </c>
       <c r="Q15">
-        <v>175.838797395</v>
+        <v>175.39983181</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1263809531087715</v>
+        <v>0.1271932322039466</v>
       </c>
       <c r="T15">
-        <v>1.109227150614509</v>
+        <v>1.120408478105493</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>31.73130303597718</v>
+        <v>29.46478139055024</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1153718796953941</v>
+        <v>0.115234180186157</v>
       </c>
       <c r="C16">
-        <v>905.0942958779533</v>
+        <v>896.0249400699776</v>
       </c>
       <c r="D16">
-        <v>979.0322958779533</v>
+        <v>980.2299400699776</v>
       </c>
       <c r="E16">
-        <v>66.13800000000003</v>
+        <v>76.40500000000003</v>
       </c>
       <c r="F16">
-        <v>143.738</v>
+        <v>154.005</v>
       </c>
       <c r="G16">
         <v>69.8</v>
@@ -2593,28 +2593,28 @@
         <v>213.031</v>
       </c>
       <c r="M16">
-        <v>7.230021400000001</v>
+        <v>7.746451500000001</v>
       </c>
       <c r="N16">
-        <v>205.8009786</v>
+        <v>205.2845485</v>
       </c>
       <c r="O16">
-        <v>30.87014679</v>
+        <v>30.792682275</v>
       </c>
       <c r="P16">
-        <v>174.93083181</v>
+        <v>174.491866225</v>
       </c>
       <c r="Q16">
-        <v>175.39983181</v>
+        <v>174.960866225</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1271932322039466</v>
+        <v>0.12802462374842</v>
       </c>
       <c r="T16">
-        <v>1.120408478105493</v>
+        <v>1.13185289565509</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>29.46478139055024</v>
+        <v>27.50046263118022</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.115234180186157</v>
+        <v>0.1150964806769199</v>
       </c>
       <c r="C17">
-        <v>896.0249400699776</v>
+        <v>886.9585179923791</v>
       </c>
       <c r="D17">
-        <v>980.2299400699776</v>
+        <v>981.4305179923792</v>
       </c>
       <c r="E17">
-        <v>76.405</v>
+        <v>86.67200000000003</v>
       </c>
       <c r="F17">
-        <v>154.005</v>
+        <v>164.272</v>
       </c>
       <c r="G17">
         <v>69.8</v>
@@ -2675,28 +2675,28 @@
         <v>213.031</v>
       </c>
       <c r="M17">
-        <v>7.746451499999999</v>
+        <v>8.2628816</v>
       </c>
       <c r="N17">
-        <v>205.2845485</v>
+        <v>204.7681184</v>
       </c>
       <c r="O17">
-        <v>30.792682275</v>
+        <v>30.71521776</v>
       </c>
       <c r="P17">
-        <v>174.491866225</v>
+        <v>174.05290064</v>
       </c>
       <c r="Q17">
-        <v>174.960866225</v>
+        <v>174.52190064</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.12802462374842</v>
+        <v>0.1288758103296666</v>
       </c>
       <c r="T17">
-        <v>1.13185289565509</v>
+        <v>1.14356979933682</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.50046263118023</v>
+        <v>25.78168371673146</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1150964806769199</v>
+        <v>0.1149587811676829</v>
       </c>
       <c r="C18">
-        <v>886.9585179923791</v>
+        <v>877.8950404380064</v>
       </c>
       <c r="D18">
-        <v>981.4305179923792</v>
+        <v>982.6340404380063</v>
       </c>
       <c r="E18">
-        <v>86.67200000000003</v>
+        <v>96.93900000000002</v>
       </c>
       <c r="F18">
-        <v>164.272</v>
+        <v>174.539</v>
       </c>
       <c r="G18">
         <v>69.8</v>
@@ -2757,28 +2757,28 @@
         <v>213.031</v>
       </c>
       <c r="M18">
-        <v>8.2628816</v>
+        <v>8.779311700000001</v>
       </c>
       <c r="N18">
-        <v>204.7681184</v>
+        <v>204.2516883</v>
       </c>
       <c r="O18">
-        <v>30.71521776</v>
+        <v>30.637753245</v>
       </c>
       <c r="P18">
-        <v>174.05290064</v>
+        <v>173.613935055</v>
       </c>
       <c r="Q18">
-        <v>174.52190064</v>
+        <v>174.082935055</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1288758103296666</v>
+        <v>0.1297475074309432</v>
       </c>
       <c r="T18">
-        <v>1.14356979933682</v>
+        <v>1.155569038047025</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.78168371673146</v>
+        <v>24.26511408633549</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1149587811676829</v>
+        <v>0.1148210816584458</v>
       </c>
       <c r="C19">
-        <v>877.8950404380064</v>
+        <v>868.8345182527137</v>
       </c>
       <c r="D19">
-        <v>982.6340404380063</v>
+        <v>983.8405182527137</v>
       </c>
       <c r="E19">
-        <v>96.93900000000002</v>
+        <v>107.206</v>
       </c>
       <c r="F19">
-        <v>174.539</v>
+        <v>184.806</v>
       </c>
       <c r="G19">
         <v>69.8</v>
@@ -2839,28 +2839,28 @@
         <v>213.031</v>
       </c>
       <c r="M19">
-        <v>8.779311700000001</v>
+        <v>9.295741800000002</v>
       </c>
       <c r="N19">
-        <v>204.2516883</v>
+        <v>203.7352582</v>
       </c>
       <c r="O19">
-        <v>30.637753245</v>
+        <v>30.56028873</v>
       </c>
       <c r="P19">
-        <v>173.613935055</v>
+        <v>173.17496947</v>
       </c>
       <c r="Q19">
-        <v>174.082935055</v>
+        <v>173.64396947</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1297475074309432</v>
+        <v>0.130640465437129</v>
       </c>
       <c r="T19">
-        <v>1.155569038047025</v>
+        <v>1.167860941116015</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.26511408633549</v>
+        <v>22.91705219265018</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1148210816584458</v>
+        <v>0.1146833821492087</v>
       </c>
       <c r="C20">
-        <v>868.8345182527137</v>
+        <v>859.7769623356875</v>
       </c>
       <c r="D20">
-        <v>983.8405182527137</v>
+        <v>985.0499623356875</v>
       </c>
       <c r="E20">
-        <v>107.206</v>
+        <v>117.473</v>
       </c>
       <c r="F20">
-        <v>184.806</v>
+        <v>195.073</v>
       </c>
       <c r="G20">
         <v>69.8</v>
@@ -2921,28 +2921,28 @@
         <v>213.031</v>
       </c>
       <c r="M20">
-        <v>9.2957418</v>
+        <v>9.812171899999999</v>
       </c>
       <c r="N20">
-        <v>203.7352582</v>
+        <v>203.2188281</v>
       </c>
       <c r="O20">
-        <v>30.56028873</v>
+        <v>30.482824215</v>
       </c>
       <c r="P20">
-        <v>173.17496947</v>
+        <v>172.736003885</v>
       </c>
       <c r="Q20">
-        <v>173.64396947</v>
+        <v>173.205003885</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.130640465437129</v>
+        <v>0.1315554717891466</v>
       </c>
       <c r="T20">
-        <v>1.167860941116015</v>
+        <v>1.180456347964487</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.91705219265019</v>
+        <v>21.71089155093176</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1146833821492087</v>
+        <v>0.1145456826399717</v>
       </c>
       <c r="C21">
-        <v>859.7769623356875</v>
+        <v>850.7223836397737</v>
       </c>
       <c r="D21">
-        <v>985.0499623356875</v>
+        <v>986.2623836397737</v>
       </c>
       <c r="E21">
-        <v>117.473</v>
+        <v>127.74</v>
       </c>
       <c r="F21">
-        <v>195.073</v>
+        <v>205.34</v>
       </c>
       <c r="G21">
         <v>69.8</v>
@@ -3003,28 +3003,28 @@
         <v>213.031</v>
       </c>
       <c r="M21">
-        <v>9.812171899999999</v>
+        <v>10.328602</v>
       </c>
       <c r="N21">
-        <v>203.2188281</v>
+        <v>202.702398</v>
       </c>
       <c r="O21">
-        <v>30.482824215</v>
+        <v>30.4053597</v>
       </c>
       <c r="P21">
-        <v>172.736003885</v>
+        <v>172.2970383</v>
       </c>
       <c r="Q21">
-        <v>173.205003885</v>
+        <v>172.7660383</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1315554717891466</v>
+        <v>0.1324933532999646</v>
       </c>
       <c r="T21">
-        <v>1.180456347964487</v>
+        <v>1.193366639984171</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.71089155093176</v>
+        <v>20.62534697338517</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1145456826399717</v>
+        <v>0.1144079831307346</v>
       </c>
       <c r="C22">
-        <v>850.7223836397737</v>
+        <v>841.6707931718088</v>
       </c>
       <c r="D22">
-        <v>986.2623836397737</v>
+        <v>987.4777931718088</v>
       </c>
       <c r="E22">
-        <v>127.74</v>
+        <v>138.007</v>
       </c>
       <c r="F22">
-        <v>205.34</v>
+        <v>215.607</v>
       </c>
       <c r="G22">
         <v>69.8</v>
@@ -3085,28 +3085,28 @@
         <v>213.031</v>
       </c>
       <c r="M22">
-        <v>10.328602</v>
+        <v>10.8450321</v>
       </c>
       <c r="N22">
-        <v>202.702398</v>
+        <v>202.1859679</v>
       </c>
       <c r="O22">
-        <v>30.4053597</v>
+        <v>30.327895185</v>
       </c>
       <c r="P22">
-        <v>172.2970383</v>
+        <v>171.858072715</v>
       </c>
       <c r="Q22">
-        <v>172.7660383</v>
+        <v>172.327072715</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1324933532999646</v>
+        <v>0.1334549786464995</v>
       </c>
       <c r="T22">
-        <v>1.193366639984171</v>
+        <v>1.206603774839796</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.62534697338517</v>
+        <v>19.64318759370016</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1144079831307346</v>
+        <v>0.1142702836214975</v>
       </c>
       <c r="C23">
-        <v>841.6707931718088</v>
+        <v>832.6222019929526</v>
       </c>
       <c r="D23">
-        <v>987.4777931718088</v>
+        <v>988.6962019929525</v>
       </c>
       <c r="E23">
-        <v>138.007</v>
+        <v>148.274</v>
       </c>
       <c r="F23">
-        <v>215.607</v>
+        <v>225.874</v>
       </c>
       <c r="G23">
         <v>69.8</v>
@@ -3167,28 +3167,28 @@
         <v>213.031</v>
       </c>
       <c r="M23">
-        <v>10.8450321</v>
+        <v>11.3614622</v>
       </c>
       <c r="N23">
-        <v>202.1859679</v>
+        <v>201.6695378</v>
       </c>
       <c r="O23">
-        <v>30.327895185</v>
+        <v>30.25043067</v>
       </c>
       <c r="P23">
-        <v>171.858072715</v>
+        <v>171.41910713</v>
       </c>
       <c r="Q23">
-        <v>172.327072715</v>
+        <v>171.88810713</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1334549786464995</v>
+        <v>0.134441261053202</v>
       </c>
       <c r="T23">
-        <v>1.206603774839796</v>
+        <v>1.220180323409668</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.64318759370016</v>
+        <v>18.75031543035015</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1142702836214975</v>
+        <v>0.1141325841122605</v>
       </c>
       <c r="C24">
-        <v>832.6222019929526</v>
+        <v>823.5766212190244</v>
       </c>
       <c r="D24">
-        <v>988.6962019929525</v>
+        <v>989.9176212190245</v>
       </c>
       <c r="E24">
-        <v>148.274</v>
+        <v>158.541</v>
       </c>
       <c r="F24">
-        <v>225.874</v>
+        <v>236.141</v>
       </c>
       <c r="G24">
         <v>69.8</v>
@@ -3249,28 +3249,28 @@
         <v>213.031</v>
       </c>
       <c r="M24">
-        <v>11.3614622</v>
+        <v>11.8778923</v>
       </c>
       <c r="N24">
-        <v>201.6695378</v>
+        <v>201.1531077</v>
       </c>
       <c r="O24">
-        <v>30.25043067</v>
+        <v>30.172966155</v>
       </c>
       <c r="P24">
-        <v>171.41910713</v>
+        <v>170.980141545</v>
       </c>
       <c r="Q24">
-        <v>171.88810713</v>
+        <v>171.449141545</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.134441261053202</v>
+        <v>0.1354531611847538</v>
       </c>
       <c r="T24">
-        <v>1.220180323409668</v>
+        <v>1.234109509604731</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.75031543035015</v>
+        <v>17.93508432468276</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1141325841122605</v>
+        <v>0.1139948846030234</v>
       </c>
       <c r="C25">
-        <v>823.5766212190244</v>
+        <v>814.5340620208407</v>
       </c>
       <c r="D25">
-        <v>989.9176212190245</v>
+        <v>991.1420620208406</v>
       </c>
       <c r="E25">
-        <v>158.541</v>
+        <v>168.808</v>
       </c>
       <c r="F25">
-        <v>236.141</v>
+        <v>246.408</v>
       </c>
       <c r="G25">
         <v>69.8</v>
@@ -3331,28 +3331,28 @@
         <v>213.031</v>
       </c>
       <c r="M25">
-        <v>11.8778923</v>
+        <v>12.3943224</v>
       </c>
       <c r="N25">
-        <v>201.1531077</v>
+        <v>200.6366776</v>
       </c>
       <c r="O25">
-        <v>30.172966155</v>
+        <v>30.09550164</v>
       </c>
       <c r="P25">
-        <v>170.980141545</v>
+        <v>170.54117596</v>
       </c>
       <c r="Q25">
-        <v>171.449141545</v>
+        <v>171.01017596</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1354531611847538</v>
+        <v>0.136491690267136</v>
       </c>
       <c r="T25">
-        <v>1.234109509604731</v>
+        <v>1.248405253331244</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.93508432468276</v>
+        <v>17.18778914448764</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1139948846030234</v>
+        <v>0.1138571850937863</v>
       </c>
       <c r="C26">
-        <v>814.5340620208407</v>
+        <v>805.4945356245548</v>
       </c>
       <c r="D26">
-        <v>991.1420620208406</v>
+        <v>992.3695356245547</v>
       </c>
       <c r="E26">
-        <v>168.808</v>
+        <v>179.075</v>
       </c>
       <c r="F26">
-        <v>246.408</v>
+        <v>256.675</v>
       </c>
       <c r="G26">
         <v>69.8</v>
@@ -3413,28 +3413,28 @@
         <v>213.031</v>
       </c>
       <c r="M26">
-        <v>12.3943224</v>
+        <v>12.9107525</v>
       </c>
       <c r="N26">
-        <v>200.6366776</v>
+        <v>200.1202475</v>
       </c>
       <c r="O26">
-        <v>30.09550164</v>
+        <v>30.018037125</v>
       </c>
       <c r="P26">
-        <v>170.54117596</v>
+        <v>170.102210375</v>
       </c>
       <c r="Q26">
-        <v>171.01017596</v>
+        <v>170.571210375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.136491690267136</v>
+        <v>0.1375579134583818</v>
       </c>
       <c r="T26">
-        <v>1.248405253331244</v>
+        <v>1.263082216890463</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.18778914448764</v>
+        <v>16.50027757870814</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1138571850937863</v>
+        <v>0.1137194855845493</v>
       </c>
       <c r="C27">
-        <v>805.4945356245548</v>
+        <v>796.458053312002</v>
       </c>
       <c r="D27">
-        <v>992.3695356245547</v>
+        <v>993.600053312002</v>
       </c>
       <c r="E27">
-        <v>179.075</v>
+        <v>189.342</v>
       </c>
       <c r="F27">
-        <v>256.675</v>
+        <v>266.942</v>
       </c>
       <c r="G27">
         <v>69.8</v>
@@ -3495,28 +3495,28 @@
         <v>213.031</v>
       </c>
       <c r="M27">
-        <v>12.9107525</v>
+        <v>13.4271826</v>
       </c>
       <c r="N27">
-        <v>200.1202475</v>
+        <v>199.6038174</v>
       </c>
       <c r="O27">
-        <v>30.018037125</v>
+        <v>29.94057261</v>
       </c>
       <c r="P27">
-        <v>170.102210375</v>
+        <v>169.66324479</v>
       </c>
       <c r="Q27">
-        <v>170.571210375</v>
+        <v>170.13224479</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1375579134583818</v>
+        <v>0.1386529534926341</v>
       </c>
       <c r="T27">
-        <v>1.263082216890463</v>
+        <v>1.278155855140472</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.50027757870814</v>
+        <v>15.86565151798859</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1137194855845493</v>
+        <v>0.1135817860753122</v>
       </c>
       <c r="C28">
-        <v>796.458053312002</v>
+        <v>787.4246264210431</v>
       </c>
       <c r="D28">
-        <v>993.600053312002</v>
+        <v>994.8336264210432</v>
       </c>
       <c r="E28">
-        <v>189.342</v>
+        <v>199.609</v>
       </c>
       <c r="F28">
-        <v>266.942</v>
+        <v>277.209</v>
       </c>
       <c r="G28">
         <v>69.8</v>
@@ -3577,28 +3577,28 @@
         <v>213.031</v>
       </c>
       <c r="M28">
-        <v>13.4271826</v>
+        <v>13.9436127</v>
       </c>
       <c r="N28">
-        <v>199.6038174</v>
+        <v>199.0873873</v>
       </c>
       <c r="O28">
-        <v>29.94057261</v>
+        <v>29.863108095</v>
       </c>
       <c r="P28">
-        <v>169.66324479</v>
+        <v>169.224279205</v>
       </c>
       <c r="Q28">
-        <v>170.13224479</v>
+        <v>169.693279205</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1386529534926341</v>
+        <v>0.1397779946237153</v>
       </c>
       <c r="T28">
-        <v>1.278155855140472</v>
+        <v>1.293642469780892</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.86565151798859</v>
+        <v>15.27803479510013</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1135817860753122</v>
+        <v>0.1134440865660751</v>
       </c>
       <c r="C29">
-        <v>787.4246264210431</v>
+        <v>778.3942663459145</v>
       </c>
       <c r="D29">
-        <v>994.8336264210432</v>
+        <v>996.0702663459147</v>
       </c>
       <c r="E29">
-        <v>199.609</v>
+        <v>209.8760000000001</v>
       </c>
       <c r="F29">
-        <v>277.209</v>
+        <v>287.4760000000001</v>
       </c>
       <c r="G29">
         <v>69.8</v>
@@ -3659,28 +3659,28 @@
         <v>213.031</v>
       </c>
       <c r="M29">
-        <v>13.9436127</v>
+        <v>14.4600428</v>
       </c>
       <c r="N29">
-        <v>199.0873873</v>
+        <v>198.5709572</v>
       </c>
       <c r="O29">
-        <v>29.863108095</v>
+        <v>29.78564358</v>
       </c>
       <c r="P29">
-        <v>169.224279205</v>
+        <v>168.78531362</v>
       </c>
       <c r="Q29">
-        <v>169.693279205</v>
+        <v>169.25431362</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1397779946237153</v>
+        <v>0.1409342868973266</v>
       </c>
       <c r="T29">
-        <v>1.293642469780892</v>
+        <v>1.309559268161324</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.27803479510013</v>
+        <v>14.73239069527512</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1134440865660751</v>
+        <v>0.1133063870568381</v>
       </c>
       <c r="C30">
-        <v>778.3942663459145</v>
+        <v>769.3669845375772</v>
       </c>
       <c r="D30">
-        <v>996.0702663459147</v>
+        <v>997.3099845375773</v>
       </c>
       <c r="E30">
-        <v>209.8760000000001</v>
+        <v>220.1430000000001</v>
       </c>
       <c r="F30">
-        <v>287.4760000000001</v>
+        <v>297.7430000000001</v>
       </c>
       <c r="G30">
         <v>69.8</v>
@@ -3741,28 +3741,28 @@
         <v>213.031</v>
       </c>
       <c r="M30">
-        <v>14.4600428</v>
+        <v>14.9764729</v>
       </c>
       <c r="N30">
-        <v>198.5709572</v>
+        <v>198.0545271</v>
       </c>
       <c r="O30">
-        <v>29.78564358</v>
+        <v>29.708179065</v>
       </c>
       <c r="P30">
-        <v>168.78531362</v>
+        <v>168.346348035</v>
       </c>
       <c r="Q30">
-        <v>169.25431362</v>
+        <v>168.815348035</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1409342868973266</v>
+        <v>0.142123150784279</v>
       </c>
       <c r="T30">
-        <v>1.309559268161324</v>
+        <v>1.325924427059515</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.73239069527512</v>
+        <v>14.22437722302425</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.113306387056838</v>
+        <v>0.113168687547601</v>
       </c>
       <c r="C31">
-        <v>769.3669845375775</v>
+        <v>760.3427925040723</v>
       </c>
       <c r="D31">
-        <v>997.3099845375775</v>
+        <v>998.5527925040723</v>
       </c>
       <c r="E31">
-        <v>220.143</v>
+        <v>230.41</v>
       </c>
       <c r="F31">
-        <v>297.743</v>
+        <v>308.01</v>
       </c>
       <c r="G31">
         <v>69.8</v>
@@ -3823,28 +3823,28 @@
         <v>213.031</v>
       </c>
       <c r="M31">
-        <v>14.9764729</v>
+        <v>15.492903</v>
       </c>
       <c r="N31">
-        <v>198.0545271</v>
+        <v>197.538097</v>
       </c>
       <c r="O31">
-        <v>29.708179065</v>
+        <v>29.63071455</v>
       </c>
       <c r="P31">
-        <v>168.346348035</v>
+        <v>167.90738245</v>
       </c>
       <c r="Q31">
-        <v>168.815348035</v>
+        <v>168.37638245</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.142123150784279</v>
+        <v>0.1433459822108585</v>
       </c>
       <c r="T31">
-        <v>1.325924427059515</v>
+        <v>1.342757161926225</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.22437722302426</v>
+        <v>13.75023131559011</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.113168687547601</v>
+        <v>0.1130309880383639</v>
       </c>
       <c r="C32">
-        <v>760.3427925040723</v>
+        <v>751.3217018108735</v>
       </c>
       <c r="D32">
-        <v>998.5527925040723</v>
+        <v>999.7987018108736</v>
       </c>
       <c r="E32">
-        <v>230.41</v>
+        <v>240.677</v>
       </c>
       <c r="F32">
-        <v>308.01</v>
+        <v>318.277</v>
       </c>
       <c r="G32">
         <v>69.8</v>
@@ -3905,28 +3905,28 @@
         <v>213.031</v>
       </c>
       <c r="M32">
-        <v>15.492903</v>
+        <v>16.0093331</v>
       </c>
       <c r="N32">
-        <v>197.538097</v>
+        <v>197.0216669</v>
       </c>
       <c r="O32">
-        <v>29.63071455</v>
+        <v>29.553250035</v>
       </c>
       <c r="P32">
-        <v>167.90738245</v>
+        <v>167.468416865</v>
       </c>
       <c r="Q32">
-        <v>168.37638245</v>
+        <v>167.937416865</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1433459822108585</v>
+        <v>0.1446042580266144</v>
       </c>
       <c r="T32">
-        <v>1.342757161926225</v>
+        <v>1.360077802151391</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.75023131559011</v>
+        <v>13.30667546670011</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1130309880383639</v>
+        <v>0.1128932885291268</v>
       </c>
       <c r="C33">
-        <v>751.3217018108735</v>
+        <v>742.3037240812512</v>
       </c>
       <c r="D33">
-        <v>999.7987018108736</v>
+        <v>1001.047724081251</v>
       </c>
       <c r="E33">
-        <v>240.677</v>
+        <v>250.944</v>
       </c>
       <c r="F33">
-        <v>318.277</v>
+        <v>328.544</v>
       </c>
       <c r="G33">
         <v>69.8</v>
@@ -3987,28 +3987,28 @@
         <v>213.031</v>
       </c>
       <c r="M33">
-        <v>16.0093331</v>
+        <v>16.5257632</v>
       </c>
       <c r="N33">
-        <v>197.0216669</v>
+        <v>196.5052368</v>
       </c>
       <c r="O33">
-        <v>29.553250035</v>
+        <v>29.47578552</v>
       </c>
       <c r="P33">
-        <v>167.468416865</v>
+        <v>167.02945128</v>
       </c>
       <c r="Q33">
-        <v>167.937416865</v>
+        <v>167.49845128</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1446042580266144</v>
+        <v>0.1458995419545983</v>
       </c>
       <c r="T33">
-        <v>1.360077802151391</v>
+        <v>1.377907872971414</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.30667546670011</v>
+        <v>12.89084185836573</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1128932885291268</v>
+        <v>0.1131763390198898</v>
       </c>
       <c r="C34">
-        <v>742.3037240812512</v>
+        <v>729.4726528125174</v>
       </c>
       <c r="D34">
-        <v>1001.047724081251</v>
+        <v>998.4836528125174</v>
       </c>
       <c r="E34">
-        <v>250.944</v>
+        <v>261.211</v>
       </c>
       <c r="F34">
-        <v>328.544</v>
+        <v>338.811</v>
       </c>
       <c r="G34">
         <v>69.8</v>
@@ -4069,45 +4069,45 @@
         <v>213.031</v>
       </c>
       <c r="M34">
-        <v>16.5257632</v>
+        <v>17.5504098</v>
       </c>
       <c r="N34">
-        <v>196.5052368</v>
+        <v>195.4805902</v>
       </c>
       <c r="O34">
-        <v>29.47578552</v>
+        <v>29.32208853</v>
       </c>
       <c r="P34">
-        <v>167.02945128</v>
+        <v>166.15850167</v>
       </c>
       <c r="Q34">
-        <v>167.49845128</v>
+        <v>166.62750167</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1458995419545983</v>
+        <v>0.1472334910744623</v>
       </c>
       <c r="T34">
-        <v>1.377907872971414</v>
+        <v>1.396270184711438</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>12.89084185836573</v>
+        <v>12.13823508554199</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1131763390198898</v>
+        <v>0.1130513895106527</v>
       </c>
       <c r="C35">
-        <v>729.4726528125174</v>
+        <v>720.3359125158008</v>
       </c>
       <c r="D35">
-        <v>998.4836528125174</v>
+        <v>999.6139125158008</v>
       </c>
       <c r="E35">
-        <v>261.211</v>
+        <v>271.4780000000001</v>
       </c>
       <c r="F35">
-        <v>338.811</v>
+        <v>349.078</v>
       </c>
       <c r="G35">
         <v>69.8</v>
@@ -4151,28 +4151,28 @@
         <v>213.031</v>
       </c>
       <c r="M35">
-        <v>17.5504098</v>
+        <v>18.0822404</v>
       </c>
       <c r="N35">
-        <v>195.4805902</v>
+        <v>194.9487596</v>
       </c>
       <c r="O35">
-        <v>29.32208853</v>
+        <v>29.24231394</v>
       </c>
       <c r="P35">
-        <v>166.15850167</v>
+        <v>165.70644566</v>
       </c>
       <c r="Q35">
-        <v>166.62750167</v>
+        <v>166.17544566</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1472334910744623</v>
+        <v>0.1486078628949283</v>
       </c>
       <c r="T35">
-        <v>1.396270184711438</v>
+        <v>1.415188930140554</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.13823508554199</v>
+        <v>11.78122817126135</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1130513895106527</v>
+        <v>0.1129264400014156</v>
       </c>
       <c r="C36">
-        <v>720.3359125158008</v>
+        <v>711.2017339730335</v>
       </c>
       <c r="D36">
-        <v>999.6139125158008</v>
+        <v>1000.746733973033</v>
       </c>
       <c r="E36">
-        <v>271.4780000000001</v>
+        <v>281.745</v>
       </c>
       <c r="F36">
-        <v>349.078</v>
+        <v>359.345</v>
       </c>
       <c r="G36">
         <v>69.8</v>
@@ -4233,28 +4233,28 @@
         <v>213.031</v>
       </c>
       <c r="M36">
-        <v>18.0822404</v>
+        <v>18.614071</v>
       </c>
       <c r="N36">
-        <v>194.9487596</v>
+        <v>194.416929</v>
       </c>
       <c r="O36">
-        <v>29.24231394</v>
+        <v>29.16253935</v>
       </c>
       <c r="P36">
-        <v>165.70644566</v>
+        <v>165.25438965</v>
       </c>
       <c r="Q36">
-        <v>166.17544566</v>
+        <v>165.72338965</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1486078628949283</v>
+        <v>0.150024523079101</v>
       </c>
       <c r="T36">
-        <v>1.415188930140554</v>
+        <v>1.434689790813643</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.78122817126135</v>
+        <v>11.44462165208245</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1129264400014156</v>
+        <v>0.1128014904921786</v>
       </c>
       <c r="C37">
-        <v>711.2017339730335</v>
+        <v>702.0701259034888</v>
       </c>
       <c r="D37">
-        <v>1000.746733973033</v>
+        <v>1001.882125903489</v>
       </c>
       <c r="E37">
-        <v>281.745</v>
+        <v>292.0120000000001</v>
       </c>
       <c r="F37">
-        <v>359.345</v>
+        <v>369.6120000000001</v>
       </c>
       <c r="G37">
         <v>69.8</v>
@@ -4315,28 +4315,28 @@
         <v>213.031</v>
       </c>
       <c r="M37">
-        <v>18.614071</v>
+        <v>19.1459016</v>
       </c>
       <c r="N37">
-        <v>194.416929</v>
+        <v>193.8850984</v>
       </c>
       <c r="O37">
-        <v>29.16253935</v>
+        <v>29.08276476</v>
       </c>
       <c r="P37">
-        <v>165.25438965</v>
+        <v>164.80233364</v>
       </c>
       <c r="Q37">
-        <v>165.72338965</v>
+        <v>165.27133364</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.150024523079101</v>
+        <v>0.151485453894029</v>
       </c>
       <c r="T37">
-        <v>1.434689790813643</v>
+        <v>1.454800053382765</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.44462165208245</v>
+        <v>11.12671549508016</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1128014904921786</v>
+        <v>0.1126765409829415</v>
       </c>
       <c r="C38">
-        <v>702.0701259034888</v>
+        <v>692.9410970660548</v>
       </c>
       <c r="D38">
-        <v>1001.882125903489</v>
+        <v>1003.020097066055</v>
       </c>
       <c r="E38">
-        <v>292.0120000000001</v>
+        <v>302.279</v>
       </c>
       <c r="F38">
-        <v>369.612</v>
+        <v>379.879</v>
       </c>
       <c r="G38">
         <v>69.8</v>
@@ -4397,28 +4397,28 @@
         <v>213.031</v>
       </c>
       <c r="M38">
-        <v>19.1459016</v>
+        <v>19.6777322</v>
       </c>
       <c r="N38">
-        <v>193.8850984</v>
+        <v>193.3532678</v>
       </c>
       <c r="O38">
-        <v>29.08276476</v>
+        <v>29.00299017</v>
       </c>
       <c r="P38">
-        <v>164.80233364</v>
+        <v>164.35027763</v>
       </c>
       <c r="Q38">
-        <v>165.27133364</v>
+        <v>164.81927763</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.151485453894029</v>
+        <v>0.1529927634649865</v>
       </c>
       <c r="T38">
-        <v>1.454800053382765</v>
+        <v>1.475548736985828</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.12671549508016</v>
+        <v>10.82599345467259</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1126765409829415</v>
+        <v>0.1125515914737044</v>
       </c>
       <c r="C39">
-        <v>692.9410970660548</v>
+        <v>683.8146562594591</v>
       </c>
       <c r="D39">
-        <v>1003.020097066055</v>
+        <v>1004.160656259459</v>
       </c>
       <c r="E39">
-        <v>302.279</v>
+        <v>312.546</v>
       </c>
       <c r="F39">
-        <v>379.879</v>
+        <v>390.146</v>
       </c>
       <c r="G39">
         <v>69.8</v>
@@ -4479,28 +4479,28 @@
         <v>213.031</v>
       </c>
       <c r="M39">
-        <v>19.6777322</v>
+        <v>20.2095628</v>
       </c>
       <c r="N39">
-        <v>193.3532678</v>
+        <v>192.8214372</v>
       </c>
       <c r="O39">
-        <v>29.00299017</v>
+        <v>28.92321558</v>
       </c>
       <c r="P39">
-        <v>164.35027763</v>
+        <v>163.89822162</v>
       </c>
       <c r="Q39">
-        <v>164.81927763</v>
+        <v>164.36722162</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1529927634649865</v>
+        <v>0.1545486959253297</v>
       </c>
       <c r="T39">
-        <v>1.475548736985828</v>
+        <v>1.496966732963184</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.82599345467259</v>
+        <v>10.54109889007594</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1125515914737044</v>
+        <v>0.1124266419644673</v>
       </c>
       <c r="C40">
-        <v>683.8146562594591</v>
+        <v>674.6908123224955</v>
       </c>
       <c r="D40">
-        <v>1004.160656259459</v>
+        <v>1005.303812322496</v>
       </c>
       <c r="E40">
-        <v>312.546</v>
+        <v>322.813</v>
       </c>
       <c r="F40">
-        <v>390.146</v>
+        <v>400.413</v>
       </c>
       <c r="G40">
         <v>69.8</v>
@@ -4561,28 +4561,28 @@
         <v>213.031</v>
       </c>
       <c r="M40">
-        <v>20.2095628</v>
+        <v>20.7413934</v>
       </c>
       <c r="N40">
-        <v>192.8214372</v>
+        <v>192.2896066</v>
       </c>
       <c r="O40">
-        <v>28.92321558</v>
+        <v>28.84344099</v>
       </c>
       <c r="P40">
-        <v>163.89822162</v>
+        <v>163.44616561</v>
       </c>
       <c r="Q40">
-        <v>164.36722162</v>
+        <v>163.91516561</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1545486959253297</v>
+        <v>0.1561556425647006</v>
       </c>
       <c r="T40">
-        <v>1.496966732963184</v>
+        <v>1.519086958316846</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.54109889007594</v>
+        <v>10.27081430315092</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1124266419644673</v>
+        <v>0.1123016924552303</v>
       </c>
       <c r="C41">
-        <v>674.6908123224955</v>
+        <v>665.5695741342538</v>
       </c>
       <c r="D41">
-        <v>1005.303812322496</v>
+        <v>1006.449574134254</v>
       </c>
       <c r="E41">
-        <v>322.813</v>
+        <v>333.08</v>
       </c>
       <c r="F41">
-        <v>400.413</v>
+        <v>410.6800000000001</v>
       </c>
       <c r="G41">
         <v>69.8</v>
@@ -4643,28 +4643,28 @@
         <v>213.031</v>
       </c>
       <c r="M41">
-        <v>20.7413934</v>
+        <v>21.273224</v>
       </c>
       <c r="N41">
-        <v>192.2896066</v>
+        <v>191.757776</v>
       </c>
       <c r="O41">
-        <v>28.84344099</v>
+        <v>28.7636664</v>
       </c>
       <c r="P41">
-        <v>163.44616561</v>
+        <v>162.9941096</v>
       </c>
       <c r="Q41">
-        <v>163.91516561</v>
+        <v>163.4631096</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1561556425647006</v>
+        <v>0.1578161540920505</v>
       </c>
       <c r="T41">
-        <v>1.519086958316846</v>
+        <v>1.54194452451563</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.27081430315092</v>
+        <v>10.01404394557214</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1123016924552303</v>
+        <v>0.1127691929459932</v>
       </c>
       <c r="C42">
-        <v>665.5695741342538</v>
+        <v>651.0290265928261</v>
       </c>
       <c r="D42">
-        <v>1006.449574134254</v>
+        <v>1002.176026592826</v>
       </c>
       <c r="E42">
-        <v>333.08</v>
+        <v>343.3470000000001</v>
       </c>
       <c r="F42">
-        <v>410.6800000000001</v>
+        <v>420.9470000000001</v>
       </c>
       <c r="G42">
         <v>69.8</v>
@@ -4725,45 +4725,45 @@
         <v>213.031</v>
       </c>
       <c r="M42">
-        <v>21.273224</v>
+        <v>22.5206645</v>
       </c>
       <c r="N42">
-        <v>191.757776</v>
+        <v>190.5103355</v>
       </c>
       <c r="O42">
-        <v>28.7636664</v>
+        <v>28.576550325</v>
       </c>
       <c r="P42">
-        <v>162.9941096</v>
+        <v>161.933785175</v>
       </c>
       <c r="Q42">
-        <v>163.4631096</v>
+        <v>162.402785175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1578161540920505</v>
+        <v>0.1595329541457512</v>
       </c>
       <c r="T42">
-        <v>1.54194452451563</v>
+        <v>1.565576923466915</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>10.01404394557214</v>
+        <v>9.459356760987225</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1127691929459932</v>
+        <v>0.1126586934367561</v>
       </c>
       <c r="C43">
-        <v>651.0290265928261</v>
+        <v>641.7688536959103</v>
       </c>
       <c r="D43">
-        <v>1002.176026592826</v>
+        <v>1003.18285369591</v>
       </c>
       <c r="E43">
-        <v>343.3470000000001</v>
+        <v>353.614</v>
       </c>
       <c r="F43">
-        <v>420.9470000000001</v>
+        <v>431.2140000000001</v>
       </c>
       <c r="G43">
         <v>69.8</v>
@@ -4807,28 +4807,28 @@
         <v>213.031</v>
       </c>
       <c r="M43">
-        <v>22.5206645</v>
+        <v>23.069949</v>
       </c>
       <c r="N43">
-        <v>190.5103355</v>
+        <v>189.961051</v>
       </c>
       <c r="O43">
-        <v>28.576550325</v>
+        <v>28.49415765</v>
       </c>
       <c r="P43">
-        <v>161.933785175</v>
+        <v>161.46689335</v>
       </c>
       <c r="Q43">
-        <v>162.402785175</v>
+        <v>161.93589335</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1595329541457512</v>
+        <v>0.1613089542013037</v>
       </c>
       <c r="T43">
-        <v>1.565576923466915</v>
+        <v>1.590024232726866</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.459356760987225</v>
+        <v>9.234133980963719</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1126586934367561</v>
+        <v>0.1125481939275191</v>
       </c>
       <c r="C44">
-        <v>641.7688536959104</v>
+        <v>632.5107058329565</v>
       </c>
       <c r="D44">
-        <v>1003.18285369591</v>
+        <v>1004.191705832956</v>
       </c>
       <c r="E44">
-        <v>353.614</v>
+        <v>363.881</v>
       </c>
       <c r="F44">
-        <v>431.214</v>
+        <v>441.481</v>
       </c>
       <c r="G44">
         <v>69.8</v>
@@ -4889,28 +4889,28 @@
         <v>213.031</v>
       </c>
       <c r="M44">
-        <v>23.069949</v>
+        <v>23.6192335</v>
       </c>
       <c r="N44">
-        <v>189.961051</v>
+        <v>189.4117665</v>
       </c>
       <c r="O44">
-        <v>28.49415765</v>
+        <v>28.411764975</v>
       </c>
       <c r="P44">
-        <v>161.46689335</v>
+        <v>161.000001525</v>
       </c>
       <c r="Q44">
-        <v>161.93589335</v>
+        <v>161.469001525</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1613089542013037</v>
+        <v>0.1631472700482791</v>
       </c>
       <c r="T44">
-        <v>1.590024232726866</v>
+        <v>1.615329342311727</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.234133980963719</v>
+        <v>9.019386679080844</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1125481939275191</v>
+        <v>0.112437694418282</v>
       </c>
       <c r="C45">
-        <v>632.5107058329565</v>
+        <v>623.2545891195493</v>
       </c>
       <c r="D45">
-        <v>1004.191705832956</v>
+        <v>1005.202589119549</v>
       </c>
       <c r="E45">
-        <v>363.881</v>
+        <v>374.148</v>
       </c>
       <c r="F45">
-        <v>441.481</v>
+        <v>451.748</v>
       </c>
       <c r="G45">
         <v>69.8</v>
@@ -4971,28 +4971,28 @@
         <v>213.031</v>
       </c>
       <c r="M45">
-        <v>23.6192335</v>
+        <v>24.168518</v>
       </c>
       <c r="N45">
-        <v>189.4117665</v>
+        <v>188.862482</v>
       </c>
       <c r="O45">
-        <v>28.411764975</v>
+        <v>28.3293723</v>
       </c>
       <c r="P45">
-        <v>161.000001525</v>
+        <v>160.5331097</v>
       </c>
       <c r="Q45">
-        <v>161.469001525</v>
+        <v>161.0021097</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1631472700482791</v>
+        <v>0.1650512400326464</v>
       </c>
       <c r="T45">
-        <v>1.615329342311727</v>
+        <v>1.641538205810332</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.019386679080844</v>
+        <v>8.814400618192641</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.112437694418282</v>
+        <v>0.1123271949090449</v>
       </c>
       <c r="C46">
-        <v>623.2545891195493</v>
+        <v>614.000509695923</v>
       </c>
       <c r="D46">
-        <v>1005.202589119549</v>
+        <v>1006.215509695923</v>
       </c>
       <c r="E46">
-        <v>374.148</v>
+        <v>384.4150000000001</v>
       </c>
       <c r="F46">
-        <v>451.748</v>
+        <v>462.015</v>
       </c>
       <c r="G46">
         <v>69.8</v>
@@ -5053,28 +5053,28 @@
         <v>213.031</v>
       </c>
       <c r="M46">
-        <v>24.168518</v>
+        <v>24.7178025</v>
       </c>
       <c r="N46">
-        <v>188.862482</v>
+        <v>188.3131975</v>
       </c>
       <c r="O46">
-        <v>28.3293723</v>
+        <v>28.246979625</v>
       </c>
       <c r="P46">
-        <v>160.5331097</v>
+        <v>160.066217875</v>
       </c>
       <c r="Q46">
-        <v>161.0021097</v>
+        <v>160.535217875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1650512400326464</v>
+        <v>0.1670244452891726</v>
       </c>
       <c r="T46">
-        <v>1.641538205810332</v>
+        <v>1.668700118890706</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.814400618192641</v>
+        <v>8.618525048899471</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1123271949090449</v>
+        <v>0.1122166953998079</v>
       </c>
       <c r="C47">
-        <v>614.000509695923</v>
+        <v>604.7484737270869</v>
       </c>
       <c r="D47">
-        <v>1006.215509695923</v>
+        <v>1007.230473727087</v>
       </c>
       <c r="E47">
-        <v>384.4150000000001</v>
+        <v>394.682</v>
       </c>
       <c r="F47">
-        <v>462.015</v>
+        <v>472.282</v>
       </c>
       <c r="G47">
         <v>69.8</v>
@@ -5135,28 +5135,28 @@
         <v>213.031</v>
       </c>
       <c r="M47">
-        <v>24.7178025</v>
+        <v>25.267087</v>
       </c>
       <c r="N47">
-        <v>188.3131975</v>
+        <v>187.763913</v>
       </c>
       <c r="O47">
-        <v>28.246979625</v>
+        <v>28.16458695</v>
       </c>
       <c r="P47">
-        <v>160.066217875</v>
+        <v>159.59932605</v>
       </c>
       <c r="Q47">
-        <v>160.535217875</v>
+        <v>160.06832605</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1670244452891726</v>
+        <v>0.1690707322218664</v>
       </c>
       <c r="T47">
-        <v>1.668700118890706</v>
+        <v>1.696868028751834</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.618525048899471</v>
+        <v>8.431165808706005</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1122166953998079</v>
+        <v>0.1121061958905708</v>
       </c>
       <c r="C48">
-        <v>604.7484737270869</v>
+        <v>595.4984874029487</v>
       </c>
       <c r="D48">
-        <v>1007.230473727087</v>
+        <v>1008.247487402949</v>
       </c>
       <c r="E48">
-        <v>394.682</v>
+        <v>404.9490000000001</v>
       </c>
       <c r="F48">
-        <v>472.282</v>
+        <v>482.549</v>
       </c>
       <c r="G48">
         <v>69.8</v>
@@ -5217,28 +5217,28 @@
         <v>213.031</v>
       </c>
       <c r="M48">
-        <v>25.267087</v>
+        <v>25.8163715</v>
       </c>
       <c r="N48">
-        <v>187.763913</v>
+        <v>187.2146285</v>
       </c>
       <c r="O48">
-        <v>28.16458695</v>
+        <v>28.082194275</v>
       </c>
       <c r="P48">
-        <v>159.59932605</v>
+        <v>159.132434225</v>
       </c>
       <c r="Q48">
-        <v>160.06832605</v>
+        <v>159.601434225</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1690707322218664</v>
+        <v>0.1711942375293789</v>
       </c>
       <c r="T48">
-        <v>1.696868028751834</v>
+        <v>1.726098878607722</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.431165808706005</v>
+        <v>8.251779302137791</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1121061958905708</v>
+        <v>0.1119956963813337</v>
       </c>
       <c r="C49">
-        <v>595.4984874029487</v>
+        <v>586.2505569384425</v>
       </c>
       <c r="D49">
-        <v>1008.247487402949</v>
+        <v>1009.266556938443</v>
       </c>
       <c r="E49">
-        <v>404.9490000000001</v>
+        <v>415.2160000000001</v>
       </c>
       <c r="F49">
-        <v>482.549</v>
+        <v>492.8160000000001</v>
       </c>
       <c r="G49">
         <v>69.8</v>
@@ -5299,28 +5299,28 @@
         <v>213.031</v>
       </c>
       <c r="M49">
-        <v>25.8163715</v>
+        <v>26.365656</v>
       </c>
       <c r="N49">
-        <v>187.2146285</v>
+        <v>186.665344</v>
       </c>
       <c r="O49">
-        <v>28.082194275</v>
+        <v>27.9998016</v>
       </c>
       <c r="P49">
-        <v>159.132434225</v>
+        <v>158.6655424</v>
       </c>
       <c r="Q49">
-        <v>159.601434225</v>
+        <v>159.1345424</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1711942375293789</v>
+        <v>0.1733994161179495</v>
       </c>
       <c r="T49">
-        <v>1.726098878607722</v>
+        <v>1.756453991919605</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.251779302137791</v>
+        <v>8.079867233343254</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1119956963813337</v>
+        <v>0.1118851968720966</v>
       </c>
       <c r="C50">
-        <v>586.2505569384425</v>
+        <v>577.0046885736547</v>
       </c>
       <c r="D50">
-        <v>1009.266556938443</v>
+        <v>1010.287688573655</v>
       </c>
       <c r="E50">
-        <v>415.216</v>
+        <v>425.4830000000001</v>
       </c>
       <c r="F50">
-        <v>492.816</v>
+        <v>503.083</v>
       </c>
       <c r="G50">
         <v>69.8</v>
@@ -5381,28 +5381,28 @@
         <v>213.031</v>
       </c>
       <c r="M50">
-        <v>26.365656</v>
+        <v>26.9149405</v>
       </c>
       <c r="N50">
-        <v>186.665344</v>
+        <v>186.1160595</v>
       </c>
       <c r="O50">
-        <v>27.9998016</v>
+        <v>27.917408925</v>
       </c>
       <c r="P50">
-        <v>158.6655424</v>
+        <v>158.198650575</v>
       </c>
       <c r="Q50">
-        <v>159.1345424</v>
+        <v>158.667650575</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1733994161179495</v>
+        <v>0.1756910722982287</v>
       </c>
       <c r="T50">
-        <v>1.756453991919605</v>
+        <v>1.787999501831954</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.079867233343254</v>
+        <v>7.914971983683189</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1118851968720966</v>
+        <v>0.1117746973628596</v>
       </c>
       <c r="C51">
-        <v>577.0046885736547</v>
+        <v>567.7608885739495</v>
       </c>
       <c r="D51">
-        <v>1010.287688573655</v>
+        <v>1011.31088857395</v>
       </c>
       <c r="E51">
-        <v>425.4830000000001</v>
+        <v>435.75</v>
       </c>
       <c r="F51">
-        <v>503.083</v>
+        <v>513.35</v>
       </c>
       <c r="G51">
         <v>69.8</v>
@@ -5463,28 +5463,28 @@
         <v>213.031</v>
       </c>
       <c r="M51">
-        <v>26.9149405</v>
+        <v>27.464225</v>
       </c>
       <c r="N51">
-        <v>186.1160595</v>
+        <v>185.566775</v>
       </c>
       <c r="O51">
-        <v>27.917408925</v>
+        <v>27.83501625</v>
       </c>
       <c r="P51">
-        <v>158.198650575</v>
+        <v>157.73175875</v>
       </c>
       <c r="Q51">
-        <v>158.667650575</v>
+        <v>158.20075875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1756910722982287</v>
+        <v>0.1780743947257192</v>
       </c>
       <c r="T51">
-        <v>1.787999501831954</v>
+        <v>1.820806832140797</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.914971983683189</v>
+        <v>7.756672544009525</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1117746973628596</v>
+        <v>0.1120109978536225</v>
       </c>
       <c r="C52">
-        <v>567.7608885739495</v>
+        <v>555.3083179353122</v>
       </c>
       <c r="D52">
-        <v>1011.31088857395</v>
+        <v>1009.125317935312</v>
       </c>
       <c r="E52">
-        <v>435.75</v>
+        <v>446.0170000000001</v>
       </c>
       <c r="F52">
-        <v>513.35</v>
+        <v>523.6170000000001</v>
       </c>
       <c r="G52">
         <v>69.8</v>
@@ -5545,45 +5545,45 @@
         <v>213.031</v>
       </c>
       <c r="M52">
-        <v>27.464225</v>
+        <v>28.43240310000001</v>
       </c>
       <c r="N52">
-        <v>185.566775</v>
+        <v>184.5985969</v>
       </c>
       <c r="O52">
-        <v>27.83501625</v>
+        <v>27.689789535</v>
       </c>
       <c r="P52">
-        <v>157.73175875</v>
+        <v>156.908807365</v>
       </c>
       <c r="Q52">
-        <v>158.20075875</v>
+        <v>157.377807365</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1780743947257192</v>
+        <v>0.1805549956196378</v>
       </c>
       <c r="T52">
-        <v>1.820806832140797</v>
+        <v>1.854953237156124</v>
       </c>
       <c r="U52">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V52">
         <v>0.15</v>
       </c>
       <c r="W52">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>7.756672544009525</v>
+        <v>7.492542900814457</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1120109978536225</v>
+        <v>0.1119072983443855</v>
       </c>
       <c r="C53">
-        <v>555.3083179353122</v>
+        <v>545.9992824569274</v>
       </c>
       <c r="D53">
-        <v>1009.125317935312</v>
+        <v>1010.083282456927</v>
       </c>
       <c r="E53">
-        <v>446.0170000000001</v>
+        <v>456.284</v>
       </c>
       <c r="F53">
-        <v>523.6170000000001</v>
+        <v>533.884</v>
       </c>
       <c r="G53">
         <v>69.8</v>
@@ -5627,28 +5627,28 @@
         <v>213.031</v>
       </c>
       <c r="M53">
-        <v>28.43240310000001</v>
+        <v>28.9899012</v>
       </c>
       <c r="N53">
-        <v>184.5985969</v>
+        <v>184.0410988</v>
       </c>
       <c r="O53">
-        <v>27.689789535</v>
+        <v>27.60616482</v>
       </c>
       <c r="P53">
-        <v>156.908807365</v>
+        <v>156.43493398</v>
       </c>
       <c r="Q53">
-        <v>157.377807365</v>
+        <v>156.90393398</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1805549956196378</v>
+        <v>0.1831389548841364</v>
       </c>
       <c r="T53">
-        <v>1.854953237156124</v>
+        <v>1.890522409047089</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.492542900814457</v>
+        <v>7.348455537337258</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1119072983443855</v>
+        <v>0.1118035988351484</v>
       </c>
       <c r="C54">
-        <v>545.9992824569274</v>
+        <v>536.6920675017354</v>
       </c>
       <c r="D54">
-        <v>1010.083282456927</v>
+        <v>1011.043067501736</v>
       </c>
       <c r="E54">
-        <v>456.284</v>
+        <v>466.551</v>
       </c>
       <c r="F54">
-        <v>533.884</v>
+        <v>544.1510000000001</v>
       </c>
       <c r="G54">
         <v>69.8</v>
@@ -5709,28 +5709,28 @@
         <v>213.031</v>
       </c>
       <c r="M54">
-        <v>28.9899012</v>
+        <v>29.54739930000001</v>
       </c>
       <c r="N54">
-        <v>184.0410988</v>
+        <v>183.4836007</v>
       </c>
       <c r="O54">
-        <v>27.60616482</v>
+        <v>27.522540105</v>
       </c>
       <c r="P54">
-        <v>156.43493398</v>
+        <v>155.961060595</v>
       </c>
       <c r="Q54">
-        <v>156.90393398</v>
+        <v>156.430060595</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1831389548841364</v>
+        <v>0.1858328698620178</v>
       </c>
       <c r="T54">
-        <v>1.890522409047089</v>
+        <v>1.927605162720649</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.348455537337258</v>
+        <v>7.209805432859195</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1118035988351484</v>
+        <v>0.1116998993259113</v>
       </c>
       <c r="C55">
-        <v>536.6920675017354</v>
+        <v>527.3866782642771</v>
       </c>
       <c r="D55">
-        <v>1011.043067501736</v>
+        <v>1012.004678264277</v>
       </c>
       <c r="E55">
-        <v>466.551</v>
+        <v>476.818</v>
       </c>
       <c r="F55">
-        <v>544.1510000000001</v>
+        <v>554.418</v>
       </c>
       <c r="G55">
         <v>69.8</v>
@@ -5791,28 +5791,28 @@
         <v>213.031</v>
       </c>
       <c r="M55">
-        <v>29.54739930000001</v>
+        <v>30.1048974</v>
       </c>
       <c r="N55">
-        <v>183.4836007</v>
+        <v>182.9261026</v>
       </c>
       <c r="O55">
-        <v>27.522540105</v>
+        <v>27.43891539</v>
       </c>
       <c r="P55">
-        <v>155.961060595</v>
+        <v>155.48718721</v>
       </c>
       <c r="Q55">
-        <v>156.430060595</v>
+        <v>155.95618721</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1858328698620178</v>
+        <v>0.1886439115780681</v>
       </c>
       <c r="T55">
-        <v>1.927605162720649</v>
+        <v>1.966300210032189</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.209805432859195</v>
+        <v>7.076290517435877</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1116998993259113</v>
+        <v>0.1115961998166742</v>
       </c>
       <c r="C56">
-        <v>527.3866782642771</v>
+        <v>518.0831199588735</v>
       </c>
       <c r="D56">
-        <v>1012.004678264277</v>
+        <v>1012.968119958874</v>
       </c>
       <c r="E56">
-        <v>476.818</v>
+        <v>487.085</v>
       </c>
       <c r="F56">
-        <v>554.418</v>
+        <v>564.6850000000001</v>
       </c>
       <c r="G56">
         <v>69.8</v>
@@ -5873,28 +5873,28 @@
         <v>213.031</v>
       </c>
       <c r="M56">
-        <v>30.1048974</v>
+        <v>30.6623955</v>
       </c>
       <c r="N56">
-        <v>182.9261026</v>
+        <v>182.3686045</v>
       </c>
       <c r="O56">
-        <v>27.43891539</v>
+        <v>27.355290675</v>
       </c>
       <c r="P56">
-        <v>155.48718721</v>
+        <v>155.013313825</v>
       </c>
       <c r="Q56">
-        <v>155.95618721</v>
+        <v>155.482313825</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1886439115780681</v>
+        <v>0.1915798884814983</v>
       </c>
       <c r="T56">
-        <v>1.966300210032189</v>
+        <v>2.006715037224242</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.076290517435877</v>
+        <v>6.947630689846134</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1115961998166742</v>
+        <v>0.1114925003074372</v>
       </c>
       <c r="C57">
-        <v>518.0831199588735</v>
+        <v>508.781397819722</v>
       </c>
       <c r="D57">
-        <v>1012.968119958874</v>
+        <v>1013.933397819722</v>
       </c>
       <c r="E57">
-        <v>487.085</v>
+        <v>497.3520000000001</v>
       </c>
       <c r="F57">
-        <v>564.6850000000001</v>
+        <v>574.9520000000001</v>
       </c>
       <c r="G57">
         <v>69.8</v>
@@ -5955,28 +5955,28 @@
         <v>213.031</v>
       </c>
       <c r="M57">
-        <v>30.6623955</v>
+        <v>31.21989360000001</v>
       </c>
       <c r="N57">
-        <v>182.3686045</v>
+        <v>181.8111064</v>
       </c>
       <c r="O57">
-        <v>27.355290675</v>
+        <v>27.27166596</v>
       </c>
       <c r="P57">
-        <v>155.013313825</v>
+        <v>154.53944044</v>
       </c>
       <c r="Q57">
-        <v>155.482313825</v>
+        <v>155.00844044</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1915798884814983</v>
+        <v>0.194649318880539</v>
       </c>
       <c r="T57">
-        <v>2.006715037224242</v>
+        <v>2.048966902015934</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.947630689846134</v>
+        <v>6.823565856098881</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1114925003074372</v>
+        <v>0.1113888007982001</v>
       </c>
       <c r="C58">
-        <v>508.781397819722</v>
+        <v>499.4815171009889</v>
       </c>
       <c r="D58">
-        <v>1013.933397819722</v>
+        <v>1014.900517100989</v>
       </c>
       <c r="E58">
-        <v>497.3520000000001</v>
+        <v>507.619</v>
       </c>
       <c r="F58">
-        <v>574.9520000000001</v>
+        <v>585.2190000000001</v>
       </c>
       <c r="G58">
         <v>69.8</v>
@@ -6037,28 +6037,28 @@
         <v>213.031</v>
       </c>
       <c r="M58">
-        <v>31.21989360000001</v>
+        <v>31.7773917</v>
       </c>
       <c r="N58">
-        <v>181.8111064</v>
+        <v>181.2536083</v>
       </c>
       <c r="O58">
-        <v>27.27166596</v>
+        <v>27.188041245</v>
       </c>
       <c r="P58">
-        <v>154.53944044</v>
+        <v>154.065567055</v>
       </c>
       <c r="Q58">
-        <v>155.00844044</v>
+        <v>154.534567055</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.194649318880539</v>
+        <v>0.1978615134841863</v>
       </c>
       <c r="T58">
-        <v>2.048966902015934</v>
+        <v>2.093183969821193</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.823565856098881</v>
+        <v>6.703854174412936</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1113888007982001</v>
+        <v>0.111285101288963</v>
       </c>
       <c r="C59">
-        <v>499.4815171009889</v>
+        <v>490.1834830769071</v>
       </c>
       <c r="D59">
-        <v>1014.900517100989</v>
+        <v>1015.869483076907</v>
       </c>
       <c r="E59">
-        <v>507.619</v>
+        <v>517.8860000000001</v>
       </c>
       <c r="F59">
-        <v>585.2190000000001</v>
+        <v>595.4860000000001</v>
       </c>
       <c r="G59">
         <v>69.8</v>
@@ -6119,28 +6119,28 @@
         <v>213.031</v>
       </c>
       <c r="M59">
-        <v>31.7773917</v>
+        <v>32.33488980000001</v>
       </c>
       <c r="N59">
-        <v>181.2536083</v>
+        <v>180.6961102</v>
       </c>
       <c r="O59">
-        <v>27.188041245</v>
+        <v>27.10441653</v>
       </c>
       <c r="P59">
-        <v>154.065567055</v>
+        <v>153.59169367</v>
       </c>
       <c r="Q59">
-        <v>154.534567055</v>
+        <v>154.06069367</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1978615134841863</v>
+        <v>0.2012266697356263</v>
       </c>
       <c r="T59">
-        <v>2.093183969821193</v>
+        <v>2.139506612283846</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.703854174412936</v>
+        <v>6.588270481750643</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.111285101288963</v>
+        <v>0.1111814017797259</v>
       </c>
       <c r="C60">
-        <v>490.1834830769072</v>
+        <v>480.8873010418703</v>
       </c>
       <c r="D60">
-        <v>1015.869483076907</v>
+        <v>1016.84030104187</v>
       </c>
       <c r="E60">
-        <v>517.886</v>
+        <v>528.153</v>
       </c>
       <c r="F60">
-        <v>595.486</v>
+        <v>605.753</v>
       </c>
       <c r="G60">
         <v>69.8</v>
@@ -6201,28 +6201,28 @@
         <v>213.031</v>
       </c>
       <c r="M60">
-        <v>32.3348898</v>
+        <v>32.8923879</v>
       </c>
       <c r="N60">
-        <v>180.6961102</v>
+        <v>180.1386121</v>
       </c>
       <c r="O60">
-        <v>27.10441653</v>
+        <v>27.020791815</v>
       </c>
       <c r="P60">
-        <v>153.59169367</v>
+        <v>153.117820285</v>
       </c>
       <c r="Q60">
-        <v>154.06069367</v>
+        <v>153.586820285</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2012266697356263</v>
+        <v>0.2047559799505511</v>
       </c>
       <c r="T60">
-        <v>2.139506612283845</v>
+        <v>2.188088895842236</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.588270481750645</v>
+        <v>6.47660488036504</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1111814017797259</v>
+        <v>0.1110777022704889</v>
       </c>
       <c r="C61">
-        <v>480.8873010418703</v>
+        <v>471.59297631053</v>
       </c>
       <c r="D61">
-        <v>1016.84030104187</v>
+        <v>1017.81297631053</v>
       </c>
       <c r="E61">
-        <v>528.153</v>
+        <v>538.42</v>
       </c>
       <c r="F61">
-        <v>605.753</v>
+        <v>616.02</v>
       </c>
       <c r="G61">
         <v>69.8</v>
@@ -6283,28 +6283,28 @@
         <v>213.031</v>
       </c>
       <c r="M61">
-        <v>32.8923879</v>
+        <v>33.449886</v>
       </c>
       <c r="N61">
-        <v>180.1386121</v>
+        <v>179.581114</v>
       </c>
       <c r="O61">
-        <v>27.020791815</v>
+        <v>26.9371671</v>
       </c>
       <c r="P61">
-        <v>153.117820285</v>
+        <v>152.6439469</v>
       </c>
       <c r="Q61">
-        <v>153.586820285</v>
+        <v>153.1129469</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2047559799505511</v>
+        <v>0.2084617556762222</v>
       </c>
       <c r="T61">
-        <v>2.188088895842236</v>
+        <v>2.239100293578547</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.47660488036504</v>
+        <v>6.36866146569229</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1110777022704889</v>
+        <v>0.1109740027612518</v>
       </c>
       <c r="C62">
-        <v>471.59297631053</v>
+        <v>462.3005142178922</v>
       </c>
       <c r="D62">
-        <v>1017.81297631053</v>
+        <v>1018.787514217892</v>
       </c>
       <c r="E62">
-        <v>538.42</v>
+        <v>548.687</v>
       </c>
       <c r="F62">
-        <v>616.02</v>
+        <v>626.287</v>
       </c>
       <c r="G62">
         <v>69.8</v>
@@ -6365,28 +6365,28 @@
         <v>213.031</v>
       </c>
       <c r="M62">
-        <v>33.449886</v>
+        <v>34.0073841</v>
       </c>
       <c r="N62">
-        <v>179.581114</v>
+        <v>179.0236159</v>
       </c>
       <c r="O62">
-        <v>26.9371671</v>
+        <v>26.853542385</v>
       </c>
       <c r="P62">
-        <v>152.6439469</v>
+        <v>152.170073515</v>
       </c>
       <c r="Q62">
-        <v>153.1129469</v>
+        <v>152.639073515</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2084617556762222</v>
+        <v>0.212357571182697</v>
       </c>
       <c r="T62">
-        <v>2.239100293578547</v>
+        <v>2.292727660429541</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.36866146569229</v>
+        <v>6.264257179369465</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1109740027612518</v>
+        <v>0.1108703032520148</v>
       </c>
       <c r="C63">
-        <v>462.3005142178922</v>
+        <v>453.0099201194154</v>
       </c>
       <c r="D63">
-        <v>1018.787514217892</v>
+        <v>1019.763920119415</v>
       </c>
       <c r="E63">
-        <v>548.687</v>
+        <v>558.954</v>
       </c>
       <c r="F63">
-        <v>626.287</v>
+        <v>636.554</v>
       </c>
       <c r="G63">
         <v>69.8</v>
@@ -6447,28 +6447,28 @@
         <v>213.031</v>
       </c>
       <c r="M63">
-        <v>34.0073841</v>
+        <v>34.5648822</v>
       </c>
       <c r="N63">
-        <v>179.0236159</v>
+        <v>178.4661178</v>
       </c>
       <c r="O63">
-        <v>26.853542385</v>
+        <v>26.76991767</v>
       </c>
       <c r="P63">
-        <v>152.170073515</v>
+        <v>151.69620013</v>
       </c>
       <c r="Q63">
-        <v>152.639073515</v>
+        <v>152.16520013</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.212357571182697</v>
+        <v>0.2164584296105652</v>
       </c>
       <c r="T63">
-        <v>2.292727660429541</v>
+        <v>2.349177520272693</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.264257179369465</v>
+        <v>6.163220773250603</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1108703032520148</v>
+        <v>0.1113021037427777</v>
       </c>
       <c r="C64">
-        <v>453.0099201194154</v>
+        <v>438.689485724548</v>
       </c>
       <c r="D64">
-        <v>1019.763920119415</v>
+        <v>1015.710485724548</v>
       </c>
       <c r="E64">
-        <v>558.954</v>
+        <v>569.221</v>
       </c>
       <c r="F64">
-        <v>636.554</v>
+        <v>646.821</v>
       </c>
       <c r="G64">
         <v>69.8</v>
@@ -6529,45 +6529,45 @@
         <v>213.031</v>
       </c>
       <c r="M64">
-        <v>34.5648822</v>
+        <v>35.76920130000001</v>
       </c>
       <c r="N64">
-        <v>178.4661178</v>
+        <v>177.2617987</v>
       </c>
       <c r="O64">
-        <v>26.76991767</v>
+        <v>26.589269805</v>
       </c>
       <c r="P64">
-        <v>151.69620013</v>
+        <v>150.672528895</v>
       </c>
       <c r="Q64">
-        <v>152.16520013</v>
+        <v>151.141528895</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2164584296105652</v>
+        <v>0.2207809560615613</v>
       </c>
       <c r="T64">
-        <v>2.349177520272693</v>
+        <v>2.408678723891149</v>
       </c>
       <c r="U64">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V64">
         <v>0.15</v>
       </c>
       <c r="W64">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>6.163220773250603</v>
+        <v>5.955710283080879</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1113021037427777</v>
+        <v>0.1112069042335406</v>
       </c>
       <c r="C65">
-        <v>438.689485724548</v>
+        <v>429.3133792004252</v>
       </c>
       <c r="D65">
-        <v>1015.710485724548</v>
+        <v>1016.601379200425</v>
       </c>
       <c r="E65">
-        <v>569.221</v>
+        <v>579.4880000000001</v>
       </c>
       <c r="F65">
-        <v>646.821</v>
+        <v>657.0880000000001</v>
       </c>
       <c r="G65">
         <v>69.8</v>
@@ -6611,28 +6611,28 @@
         <v>213.031</v>
       </c>
       <c r="M65">
-        <v>35.76920130000001</v>
+        <v>36.33696640000001</v>
       </c>
       <c r="N65">
-        <v>177.2617987</v>
+        <v>176.6940336</v>
       </c>
       <c r="O65">
-        <v>26.589269805</v>
+        <v>26.50410504</v>
       </c>
       <c r="P65">
-        <v>150.672528895</v>
+        <v>150.18992856</v>
       </c>
       <c r="Q65">
-        <v>151.141528895</v>
+        <v>150.65892856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2207809560615613</v>
+        <v>0.2253436228709461</v>
       </c>
       <c r="T65">
-        <v>2.408678723891149</v>
+        <v>2.471485549932854</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.955710283080879</v>
+        <v>5.862652309907741</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1112069042335406</v>
+        <v>0.1111117047243036</v>
       </c>
       <c r="C66">
-        <v>429.3133792004252</v>
+        <v>419.9388368778448</v>
       </c>
       <c r="D66">
-        <v>1016.601379200425</v>
+        <v>1017.493836877845</v>
       </c>
       <c r="E66">
-        <v>579.4880000000001</v>
+        <v>589.755</v>
       </c>
       <c r="F66">
-        <v>657.0880000000001</v>
+        <v>667.355</v>
       </c>
       <c r="G66">
         <v>69.8</v>
@@ -6693,28 +6693,28 @@
         <v>213.031</v>
       </c>
       <c r="M66">
-        <v>36.33696640000001</v>
+        <v>36.9047315</v>
       </c>
       <c r="N66">
-        <v>176.6940336</v>
+        <v>176.1262685</v>
       </c>
       <c r="O66">
-        <v>26.50410504</v>
+        <v>26.418940275</v>
       </c>
       <c r="P66">
-        <v>150.18992856</v>
+        <v>149.707328225</v>
       </c>
       <c r="Q66">
-        <v>150.65892856</v>
+        <v>150.176328225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2253436228709461</v>
+        <v>0.2301670134980101</v>
       </c>
       <c r="T66">
-        <v>2.471485549932854</v>
+        <v>2.537881337462656</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.862652309907741</v>
+        <v>5.772457658986084</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1111117047243036</v>
+        <v>0.1110165052150665</v>
       </c>
       <c r="C67">
-        <v>419.9388368778448</v>
+        <v>410.5658628799861</v>
       </c>
       <c r="D67">
-        <v>1017.493836877845</v>
+        <v>1018.387862879986</v>
       </c>
       <c r="E67">
-        <v>589.755</v>
+        <v>600.022</v>
       </c>
       <c r="F67">
-        <v>667.355</v>
+        <v>677.6220000000001</v>
       </c>
       <c r="G67">
         <v>69.8</v>
@@ -6775,28 +6775,28 @@
         <v>213.031</v>
       </c>
       <c r="M67">
-        <v>36.9047315</v>
+        <v>37.47249660000001</v>
       </c>
       <c r="N67">
-        <v>176.1262685</v>
+        <v>175.5585034</v>
       </c>
       <c r="O67">
-        <v>26.418940275</v>
+        <v>26.33377551</v>
       </c>
       <c r="P67">
-        <v>149.707328225</v>
+        <v>149.22472789</v>
       </c>
       <c r="Q67">
-        <v>150.176328225</v>
+        <v>149.69372789</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2301670134980101</v>
+        <v>0.2352741329854897</v>
       </c>
       <c r="T67">
-        <v>2.537881337462656</v>
+        <v>2.608182759553034</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.772457658986084</v>
+        <v>5.684996179304476</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1110165052150665</v>
+        <v>0.1109213057058294</v>
       </c>
       <c r="C68">
-        <v>410.5658628799861</v>
+        <v>401.1944613445335</v>
       </c>
       <c r="D68">
-        <v>1018.387862879986</v>
+        <v>1019.283461344534</v>
       </c>
       <c r="E68">
-        <v>600.022</v>
+        <v>610.2890000000001</v>
       </c>
       <c r="F68">
-        <v>677.6220000000001</v>
+        <v>687.8890000000001</v>
       </c>
       <c r="G68">
         <v>69.8</v>
@@ -6857,28 +6857,28 @@
         <v>213.031</v>
       </c>
       <c r="M68">
-        <v>37.47249660000001</v>
+        <v>38.04026170000001</v>
       </c>
       <c r="N68">
-        <v>175.5585034</v>
+        <v>174.9907383</v>
       </c>
       <c r="O68">
-        <v>26.33377551</v>
+        <v>26.248610745</v>
       </c>
       <c r="P68">
-        <v>149.22472789</v>
+        <v>148.742127555</v>
       </c>
       <c r="Q68">
-        <v>149.69372789</v>
+        <v>149.211127555</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2352741329854897</v>
+        <v>0.2406907748661497</v>
       </c>
       <c r="T68">
-        <v>2.608182759553034</v>
+        <v>2.682744873891314</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.684996179304476</v>
+        <v>5.600145490061125</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1109213057058294</v>
+        <v>0.1108261061965923</v>
       </c>
       <c r="C69">
-        <v>401.1944613445335</v>
+        <v>391.8246364237403</v>
       </c>
       <c r="D69">
-        <v>1019.283461344534</v>
+        <v>1020.18063642374</v>
       </c>
       <c r="E69">
-        <v>610.2890000000001</v>
+        <v>620.556</v>
       </c>
       <c r="F69">
-        <v>687.8890000000001</v>
+        <v>698.1560000000001</v>
       </c>
       <c r="G69">
         <v>69.8</v>
@@ -6939,28 +6939,28 @@
         <v>213.031</v>
       </c>
       <c r="M69">
-        <v>38.04026170000001</v>
+        <v>38.6080268</v>
       </c>
       <c r="N69">
-        <v>174.9907383</v>
+        <v>174.4229732</v>
       </c>
       <c r="O69">
-        <v>26.248610745</v>
+        <v>26.16344598</v>
       </c>
       <c r="P69">
-        <v>148.742127555</v>
+        <v>148.25952722</v>
       </c>
       <c r="Q69">
-        <v>149.211127555</v>
+        <v>148.72852722</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2406907748661497</v>
+        <v>0.2464459568643511</v>
       </c>
       <c r="T69">
-        <v>2.682744873891314</v>
+        <v>2.761967120375737</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.600145490061125</v>
+        <v>5.517790409324933</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1108261061965923</v>
+        <v>0.1107309066873553</v>
       </c>
       <c r="C70">
-        <v>391.8246364237403</v>
+        <v>382.4563922844906</v>
       </c>
       <c r="D70">
-        <v>1020.18063642374</v>
+        <v>1021.079392284491</v>
       </c>
       <c r="E70">
-        <v>620.556</v>
+        <v>630.8230000000001</v>
       </c>
       <c r="F70">
-        <v>698.1560000000001</v>
+        <v>708.4230000000001</v>
       </c>
       <c r="G70">
         <v>69.8</v>
@@ -7021,28 +7021,28 @@
         <v>213.031</v>
       </c>
       <c r="M70">
-        <v>38.6080268</v>
+        <v>39.17579190000001</v>
       </c>
       <c r="N70">
-        <v>174.4229732</v>
+        <v>173.8552081</v>
       </c>
       <c r="O70">
-        <v>26.16344598</v>
+        <v>26.078281215</v>
       </c>
       <c r="P70">
-        <v>148.25952722</v>
+        <v>147.776926885</v>
       </c>
       <c r="Q70">
-        <v>148.72852722</v>
+        <v>148.245926885</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2464459568643511</v>
+        <v>0.2525724409269525</v>
       </c>
       <c r="T70">
-        <v>2.761967120375737</v>
+        <v>2.846300479536574</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.517790409324933</v>
+        <v>5.437822432378194</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1107309066873553</v>
+        <v>0.1106357071781182</v>
       </c>
       <c r="C71">
-        <v>382.4563922844906</v>
+        <v>373.0897331083656</v>
       </c>
       <c r="D71">
-        <v>1021.079392284491</v>
+        <v>1021.979733108366</v>
       </c>
       <c r="E71">
-        <v>630.8230000000001</v>
+        <v>641.09</v>
       </c>
       <c r="F71">
-        <v>708.4230000000001</v>
+        <v>718.6900000000001</v>
       </c>
       <c r="G71">
         <v>69.8</v>
@@ -7103,28 +7103,28 @@
         <v>213.031</v>
       </c>
       <c r="M71">
-        <v>39.17579190000001</v>
+        <v>39.743557</v>
       </c>
       <c r="N71">
-        <v>173.8552081</v>
+        <v>173.287443</v>
       </c>
       <c r="O71">
-        <v>26.078281215</v>
+        <v>25.99311645</v>
       </c>
       <c r="P71">
-        <v>147.776926885</v>
+        <v>147.29432655</v>
       </c>
       <c r="Q71">
-        <v>148.245926885</v>
+        <v>147.76332655</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2525724409269525</v>
+        <v>0.259107357260394</v>
       </c>
       <c r="T71">
-        <v>2.846300479536574</v>
+        <v>2.936256062641466</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.437822432378194</v>
+        <v>5.360139254772792</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1106357071781182</v>
+        <v>0.1105405076688811</v>
       </c>
       <c r="C72">
-        <v>373.0897331083656</v>
+        <v>363.7246630917082</v>
       </c>
       <c r="D72">
-        <v>1021.979733108366</v>
+        <v>1022.881663091708</v>
       </c>
       <c r="E72">
-        <v>641.09</v>
+        <v>651.3570000000001</v>
       </c>
       <c r="F72">
-        <v>718.6900000000001</v>
+        <v>728.9570000000001</v>
       </c>
       <c r="G72">
         <v>69.8</v>
@@ -7185,28 +7185,28 @@
         <v>213.031</v>
       </c>
       <c r="M72">
-        <v>39.743557</v>
+        <v>40.31132210000001</v>
       </c>
       <c r="N72">
-        <v>173.287443</v>
+        <v>172.7196779</v>
       </c>
       <c r="O72">
-        <v>25.99311645</v>
+        <v>25.907951685</v>
       </c>
       <c r="P72">
-        <v>147.29432655</v>
+        <v>146.811726215</v>
       </c>
       <c r="Q72">
-        <v>147.76332655</v>
+        <v>147.280726215</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.259107357260394</v>
+        <v>0.2660929574789005</v>
       </c>
       <c r="T72">
-        <v>2.936256062641466</v>
+        <v>3.032415479063938</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.360139254772792</v>
+        <v>5.284644335691485</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1105405076688811</v>
+        <v>0.110445308159644</v>
       </c>
       <c r="C73">
-        <v>363.7246630917083</v>
+        <v>354.3611864456881</v>
       </c>
       <c r="D73">
-        <v>1022.881663091708</v>
+        <v>1023.785186445688</v>
       </c>
       <c r="E73">
-        <v>651.357</v>
+        <v>661.624</v>
       </c>
       <c r="F73">
-        <v>728.957</v>
+        <v>739.224</v>
       </c>
       <c r="G73">
         <v>69.8</v>
@@ -7267,28 +7267,28 @@
         <v>213.031</v>
       </c>
       <c r="M73">
-        <v>40.3113221</v>
+        <v>40.8790872</v>
       </c>
       <c r="N73">
-        <v>172.7196779</v>
+        <v>172.1519128</v>
       </c>
       <c r="O73">
-        <v>25.907951685</v>
+        <v>25.82278692</v>
       </c>
       <c r="P73">
-        <v>146.811726215</v>
+        <v>146.32912588</v>
       </c>
       <c r="Q73">
-        <v>147.280726215</v>
+        <v>146.79812588</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2660929574789004</v>
+        <v>0.2735775291415859</v>
       </c>
       <c r="T73">
-        <v>3.032415479063937</v>
+        <v>3.13544342523087</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.284644335691486</v>
+        <v>5.21124649769577</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.110445308159644</v>
+        <v>0.110350108650407</v>
       </c>
       <c r="C74">
-        <v>354.3611864456881</v>
+        <v>344.9993073963665</v>
       </c>
       <c r="D74">
-        <v>1023.785186445688</v>
+        <v>1024.690307396367</v>
       </c>
       <c r="E74">
-        <v>661.624</v>
+        <v>671.891</v>
       </c>
       <c r="F74">
-        <v>739.224</v>
+        <v>749.491</v>
       </c>
       <c r="G74">
         <v>69.8</v>
@@ -7349,28 +7349,28 @@
         <v>213.031</v>
       </c>
       <c r="M74">
-        <v>40.8790872</v>
+        <v>41.4468523</v>
       </c>
       <c r="N74">
-        <v>172.1519128</v>
+        <v>171.5841477</v>
       </c>
       <c r="O74">
-        <v>25.82278692</v>
+        <v>25.737622155</v>
       </c>
       <c r="P74">
-        <v>146.32912588</v>
+        <v>145.846525545</v>
       </c>
       <c r="Q74">
-        <v>146.79812588</v>
+        <v>146.315525545</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2735775291415859</v>
+        <v>0.2816165135200258</v>
       </c>
       <c r="T74">
-        <v>3.13544342523087</v>
+        <v>3.246103071113873</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.21124649769577</v>
+        <v>5.139859559371171</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.110350108650407</v>
+        <v>0.1102549091411699</v>
       </c>
       <c r="C75">
-        <v>344.9993073963665</v>
+        <v>335.6390301847639</v>
       </c>
       <c r="D75">
-        <v>1024.690307396367</v>
+        <v>1025.597030184764</v>
       </c>
       <c r="E75">
-        <v>671.891</v>
+        <v>682.158</v>
       </c>
       <c r="F75">
-        <v>749.491</v>
+        <v>759.758</v>
       </c>
       <c r="G75">
         <v>69.8</v>
@@ -7431,28 +7431,28 @@
         <v>213.031</v>
       </c>
       <c r="M75">
-        <v>41.4468523</v>
+        <v>42.01461740000001</v>
       </c>
       <c r="N75">
-        <v>171.5841477</v>
+        <v>171.0163826</v>
       </c>
       <c r="O75">
-        <v>25.737622155</v>
+        <v>25.65245739</v>
       </c>
       <c r="P75">
-        <v>145.846525545</v>
+        <v>145.36392521</v>
       </c>
       <c r="Q75">
-        <v>146.315525545</v>
+        <v>145.83292521</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2816165135200258</v>
+        <v>0.290273881312192</v>
       </c>
       <c r="T75">
-        <v>3.246103071113873</v>
+        <v>3.365274997449415</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.139859559371171</v>
+        <v>5.070401997758046</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1102549091411699</v>
+        <v>0.1101597096319328</v>
       </c>
       <c r="C76">
-        <v>335.6390301847639</v>
+        <v>326.2803590669243</v>
       </c>
       <c r="D76">
-        <v>1025.597030184764</v>
+        <v>1026.505359066924</v>
       </c>
       <c r="E76">
-        <v>682.158</v>
+        <v>692.4250000000001</v>
       </c>
       <c r="F76">
-        <v>759.758</v>
+        <v>770.0250000000001</v>
       </c>
       <c r="G76">
         <v>69.8</v>
@@ -7513,28 +7513,28 @@
         <v>213.031</v>
       </c>
       <c r="M76">
-        <v>42.01461740000001</v>
+        <v>42.58238250000001</v>
       </c>
       <c r="N76">
-        <v>171.0163826</v>
+        <v>170.4486175</v>
       </c>
       <c r="O76">
-        <v>25.65245739</v>
+        <v>25.567292625</v>
       </c>
       <c r="P76">
-        <v>145.36392521</v>
+        <v>144.881324875</v>
       </c>
       <c r="Q76">
-        <v>145.83292521</v>
+        <v>145.350324875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.290273881312192</v>
+        <v>0.2996238385277314</v>
       </c>
       <c r="T76">
-        <v>3.365274997449415</v>
+        <v>3.4939806778918</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.070401997758046</v>
+        <v>5.002796637787939</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1101597096319328</v>
+        <v>0.1100645101226958</v>
       </c>
       <c r="C77">
-        <v>326.2803590669243</v>
+        <v>316.9232983139829</v>
       </c>
       <c r="D77">
-        <v>1026.505359066924</v>
+        <v>1027.415298313983</v>
       </c>
       <c r="E77">
-        <v>692.4250000000001</v>
+        <v>702.692</v>
       </c>
       <c r="F77">
-        <v>770.0250000000001</v>
+        <v>780.292</v>
       </c>
       <c r="G77">
         <v>69.8</v>
@@ -7595,28 +7595,28 @@
         <v>213.031</v>
       </c>
       <c r="M77">
-        <v>42.58238250000001</v>
+        <v>43.1501476</v>
       </c>
       <c r="N77">
-        <v>170.4486175</v>
+        <v>169.8808524</v>
       </c>
       <c r="O77">
-        <v>25.567292625</v>
+        <v>25.48212786</v>
       </c>
       <c r="P77">
-        <v>144.881324875</v>
+        <v>144.39872454</v>
       </c>
       <c r="Q77">
-        <v>145.350324875</v>
+        <v>144.86772454</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2996238385277314</v>
+        <v>0.3097529588445658</v>
       </c>
       <c r="T77">
-        <v>3.4939806778918</v>
+        <v>3.633411831704384</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.002796637787939</v>
+        <v>4.936970366238098</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1100645101226958</v>
+        <v>0.1099693106134587</v>
       </c>
       <c r="C78">
-        <v>316.9232983139829</v>
+        <v>307.5678522122336</v>
       </c>
       <c r="D78">
-        <v>1027.415298313983</v>
+        <v>1028.326852212234</v>
       </c>
       <c r="E78">
-        <v>702.692</v>
+        <v>712.9590000000001</v>
       </c>
       <c r="F78">
-        <v>780.292</v>
+        <v>790.5590000000001</v>
       </c>
       <c r="G78">
         <v>69.8</v>
@@ -7677,28 +7677,28 @@
         <v>213.031</v>
       </c>
       <c r="M78">
-        <v>43.1501476</v>
+        <v>43.71791270000001</v>
       </c>
       <c r="N78">
-        <v>169.8808524</v>
+        <v>169.3130873</v>
       </c>
       <c r="O78">
-        <v>25.48212786</v>
+        <v>25.396963095</v>
       </c>
       <c r="P78">
-        <v>144.39872454</v>
+        <v>143.916124205</v>
       </c>
       <c r="Q78">
-        <v>144.86772454</v>
+        <v>144.385124205</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3097529588445658</v>
+        <v>0.3207628722324292</v>
       </c>
       <c r="T78">
-        <v>3.633411831704384</v>
+        <v>3.784967433674583</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.936970366238098</v>
+        <v>4.872853867975266</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1099693106134587</v>
+        <v>0.1098741111042216</v>
       </c>
       <c r="C79">
-        <v>307.5678522122336</v>
+        <v>298.2140250631942</v>
       </c>
       <c r="D79">
-        <v>1028.326852212234</v>
+        <v>1029.240025063194</v>
       </c>
       <c r="E79">
-        <v>712.9590000000001</v>
+        <v>723.226</v>
       </c>
       <c r="F79">
-        <v>790.5590000000001</v>
+        <v>800.826</v>
       </c>
       <c r="G79">
         <v>69.8</v>
@@ -7759,28 +7759,28 @@
         <v>213.031</v>
       </c>
       <c r="M79">
-        <v>43.71791270000001</v>
+        <v>44.2856778</v>
       </c>
       <c r="N79">
-        <v>169.3130873</v>
+        <v>168.7453222</v>
       </c>
       <c r="O79">
-        <v>25.396963095</v>
+        <v>25.31179833</v>
       </c>
       <c r="P79">
-        <v>143.916124205</v>
+        <v>143.43352387</v>
       </c>
       <c r="Q79">
-        <v>144.385124205</v>
+        <v>143.90252387</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3207628722324292</v>
+        <v>0.3327736868373711</v>
       </c>
       <c r="T79">
-        <v>3.784967433674583</v>
+        <v>3.950300817642074</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.872853867975266</v>
+        <v>4.810381382488403</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1098741111042216</v>
+        <v>0.1097789115949846</v>
       </c>
       <c r="C80">
-        <v>298.2140250631942</v>
+        <v>288.8618211836758</v>
       </c>
       <c r="D80">
-        <v>1029.240025063194</v>
+        <v>1030.154821183676</v>
       </c>
       <c r="E80">
-        <v>723.226</v>
+        <v>733.4930000000001</v>
       </c>
       <c r="F80">
-        <v>800.826</v>
+        <v>811.0930000000001</v>
       </c>
       <c r="G80">
         <v>69.8</v>
@@ -7841,28 +7841,28 @@
         <v>213.031</v>
       </c>
       <c r="M80">
-        <v>44.2856778</v>
+        <v>44.8534429</v>
       </c>
       <c r="N80">
-        <v>168.7453222</v>
+        <v>168.1775571</v>
       </c>
       <c r="O80">
-        <v>25.31179833</v>
+        <v>25.226633565</v>
       </c>
       <c r="P80">
-        <v>143.43352387</v>
+        <v>142.950923535</v>
       </c>
       <c r="Q80">
-        <v>143.90252387</v>
+        <v>143.419923535</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3327736868373711</v>
+        <v>0.3459283885475455</v>
       </c>
       <c r="T80">
-        <v>3.950300817642074</v>
+        <v>4.131380238177896</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.810381382488403</v>
+        <v>4.7494904789126</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1097789115949846</v>
+        <v>0.1096837120857475</v>
       </c>
       <c r="C81">
-        <v>288.8618211836758</v>
+        <v>279.5112449058508</v>
       </c>
       <c r="D81">
-        <v>1030.154821183676</v>
+        <v>1031.071244905851</v>
       </c>
       <c r="E81">
-        <v>733.4930000000001</v>
+        <v>743.7600000000001</v>
       </c>
       <c r="F81">
-        <v>811.0930000000001</v>
+        <v>821.3600000000001</v>
       </c>
       <c r="G81">
         <v>69.8</v>
@@ -7923,28 +7923,28 @@
         <v>213.031</v>
       </c>
       <c r="M81">
-        <v>44.8534429</v>
+        <v>45.42120800000001</v>
       </c>
       <c r="N81">
-        <v>168.1775571</v>
+        <v>167.609792</v>
       </c>
       <c r="O81">
-        <v>25.226633565</v>
+        <v>25.1414688</v>
       </c>
       <c r="P81">
-        <v>142.950923535</v>
+        <v>142.4683232</v>
       </c>
       <c r="Q81">
-        <v>143.419923535</v>
+        <v>142.9373232</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3459283885475455</v>
+        <v>0.3603985604287375</v>
       </c>
       <c r="T81">
-        <v>4.131380238177896</v>
+        <v>4.330567600767302</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.7494904789126</v>
+        <v>4.690121847926193</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1096837120857475</v>
+        <v>0.1095885125765104</v>
       </c>
       <c r="C82">
-        <v>279.5112449058508</v>
+        <v>270.1623005773209</v>
       </c>
       <c r="D82">
-        <v>1031.071244905851</v>
+        <v>1031.989300577321</v>
       </c>
       <c r="E82">
-        <v>743.7600000000001</v>
+        <v>754.027</v>
       </c>
       <c r="F82">
-        <v>821.3600000000001</v>
+        <v>831.6270000000001</v>
       </c>
       <c r="G82">
         <v>69.8</v>
@@ -8005,28 +8005,28 @@
         <v>213.031</v>
       </c>
       <c r="M82">
-        <v>45.42120800000001</v>
+        <v>45.9889731</v>
       </c>
       <c r="N82">
-        <v>167.609792</v>
+        <v>167.0420269</v>
       </c>
       <c r="O82">
-        <v>25.1414688</v>
+        <v>25.056304035</v>
       </c>
       <c r="P82">
-        <v>142.4683232</v>
+        <v>141.985722865</v>
       </c>
       <c r="Q82">
-        <v>142.9373232</v>
+        <v>142.454722865</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3603985604287375</v>
+        <v>0.3763919082974234</v>
       </c>
       <c r="T82">
-        <v>4.330567600767302</v>
+        <v>4.550722054155592</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.690121847926193</v>
+        <v>4.632219109062907</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1095885125765104</v>
+        <v>0.1094933130672734</v>
       </c>
       <c r="C83">
-        <v>270.1623005773209</v>
+        <v>260.8149925611857</v>
       </c>
       <c r="D83">
-        <v>1031.989300577321</v>
+        <v>1032.908992561186</v>
       </c>
       <c r="E83">
-        <v>754.027</v>
+        <v>764.2940000000001</v>
       </c>
       <c r="F83">
-        <v>831.6270000000001</v>
+        <v>841.8940000000001</v>
       </c>
       <c r="G83">
         <v>69.8</v>
@@ -8087,28 +8087,28 @@
         <v>213.031</v>
       </c>
       <c r="M83">
-        <v>45.9889731</v>
+        <v>46.55673820000001</v>
       </c>
       <c r="N83">
-        <v>167.0420269</v>
+        <v>166.4742618</v>
       </c>
       <c r="O83">
-        <v>25.056304035</v>
+        <v>24.97113927</v>
       </c>
       <c r="P83">
-        <v>141.985722865</v>
+        <v>141.50312253</v>
       </c>
       <c r="Q83">
-        <v>142.454722865</v>
+        <v>141.97212253</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3763919082974234</v>
+        <v>0.3941622948181854</v>
       </c>
       <c r="T83">
-        <v>4.550722054155592</v>
+        <v>4.795338113475915</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.632219109062907</v>
+        <v>4.575728632123115</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1094933130672734</v>
+        <v>0.1093981135580363</v>
       </c>
       <c r="C84">
-        <v>260.8149925611857</v>
+        <v>251.4693252361114</v>
       </c>
       <c r="D84">
-        <v>1032.908992561186</v>
+        <v>1033.830325236112</v>
       </c>
       <c r="E84">
-        <v>764.2940000000001</v>
+        <v>774.561</v>
       </c>
       <c r="F84">
-        <v>841.8940000000001</v>
+        <v>852.1610000000001</v>
       </c>
       <c r="G84">
         <v>69.8</v>
@@ -8169,28 +8169,28 @@
         <v>213.031</v>
       </c>
       <c r="M84">
-        <v>46.55673820000001</v>
+        <v>47.12450330000001</v>
       </c>
       <c r="N84">
-        <v>166.4742618</v>
+        <v>165.9064967</v>
       </c>
       <c r="O84">
-        <v>24.97113927</v>
+        <v>24.885974505</v>
       </c>
       <c r="P84">
-        <v>141.50312253</v>
+        <v>141.020522195</v>
       </c>
       <c r="Q84">
-        <v>141.97212253</v>
+        <v>141.489522195</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3941622948181854</v>
+        <v>0.4140233150472725</v>
       </c>
       <c r="T84">
-        <v>4.795338113475915</v>
+        <v>5.068732532716275</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.575728632123115</v>
+        <v>4.520599371495125</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1093981135580363</v>
+        <v>0.1110879140487992</v>
       </c>
       <c r="C85">
-        <v>251.4693252361114</v>
+        <v>225.0891098096502</v>
       </c>
       <c r="D85">
-        <v>1033.830325236112</v>
+        <v>1017.71710980965</v>
       </c>
       <c r="E85">
-        <v>774.561</v>
+        <v>784.8280000000001</v>
       </c>
       <c r="F85">
-        <v>852.1610000000001</v>
+        <v>862.4280000000001</v>
       </c>
       <c r="G85">
         <v>69.8</v>
@@ -8251,45 +8251,45 @@
         <v>213.031</v>
       </c>
       <c r="M85">
-        <v>47.12450330000001</v>
+        <v>49.84833840000001</v>
       </c>
       <c r="N85">
-        <v>165.9064967</v>
+        <v>163.1826616</v>
       </c>
       <c r="O85">
-        <v>24.885974505</v>
+        <v>24.47739924</v>
       </c>
       <c r="P85">
-        <v>141.020522195</v>
+        <v>138.70526236</v>
       </c>
       <c r="Q85">
-        <v>141.489522195</v>
+        <v>139.17426236</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4140233150472725</v>
+        <v>0.4363669628049953</v>
       </c>
       <c r="T85">
-        <v>5.068732532716275</v>
+        <v>5.376301254361681</v>
       </c>
       <c r="U85">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V85">
         <v>0.15</v>
       </c>
       <c r="W85">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>4.520599371495125</v>
+        <v>4.273582768006565</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1110879140487992</v>
+        <v>0.1110139645395622</v>
       </c>
       <c r="C86">
-        <v>225.0891098096503</v>
+        <v>215.5167440858569</v>
       </c>
       <c r="D86">
-        <v>1017.71710980965</v>
+        <v>1018.411744085857</v>
       </c>
       <c r="E86">
-        <v>784.828</v>
+        <v>795.095</v>
       </c>
       <c r="F86">
-        <v>862.428</v>
+        <v>872.6950000000001</v>
       </c>
       <c r="G86">
         <v>69.8</v>
@@ -8333,28 +8333,28 @@
         <v>213.031</v>
       </c>
       <c r="M86">
-        <v>49.8483384</v>
+        <v>50.44177100000001</v>
       </c>
       <c r="N86">
-        <v>163.1826616</v>
+        <v>162.589229</v>
       </c>
       <c r="O86">
-        <v>24.47739924</v>
+        <v>24.38838435</v>
       </c>
       <c r="P86">
-        <v>138.70526236</v>
+        <v>138.20084465</v>
       </c>
       <c r="Q86">
-        <v>139.17426236</v>
+        <v>138.66984465</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4363669628049952</v>
+        <v>0.461689763597081</v>
       </c>
       <c r="T86">
-        <v>5.376301254361678</v>
+        <v>5.724879138893137</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.273582768006566</v>
+        <v>4.223305323677076</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1110139645395622</v>
+        <v>0.1109400150303251</v>
       </c>
       <c r="C87">
-        <v>215.5167440858569</v>
+        <v>205.9453272433118</v>
       </c>
       <c r="D87">
-        <v>1018.411744085857</v>
+        <v>1019.107327243312</v>
       </c>
       <c r="E87">
-        <v>795.095</v>
+        <v>805.362</v>
       </c>
       <c r="F87">
-        <v>872.6950000000001</v>
+        <v>882.962</v>
       </c>
       <c r="G87">
         <v>69.8</v>
@@ -8415,28 +8415,28 @@
         <v>213.031</v>
       </c>
       <c r="M87">
-        <v>50.44177100000001</v>
+        <v>51.0352036</v>
       </c>
       <c r="N87">
-        <v>162.589229</v>
+        <v>161.9957964</v>
       </c>
       <c r="O87">
-        <v>24.38838435</v>
+        <v>24.29936946</v>
       </c>
       <c r="P87">
-        <v>138.20084465</v>
+        <v>137.69642694</v>
       </c>
       <c r="Q87">
-        <v>138.66984465</v>
+        <v>138.16542694</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.461689763597081</v>
+        <v>0.4906301073594648</v>
       </c>
       <c r="T87">
-        <v>5.724879138893137</v>
+        <v>6.123253864071946</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.223305323677076</v>
+        <v>4.174197122238972</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1109400150303251</v>
+        <v>0.110866065521088</v>
       </c>
       <c r="C88">
-        <v>205.9453272433118</v>
+        <v>196.3748612276224</v>
       </c>
       <c r="D88">
-        <v>1019.107327243312</v>
+        <v>1019.803861227623</v>
       </c>
       <c r="E88">
-        <v>805.362</v>
+        <v>815.629</v>
       </c>
       <c r="F88">
-        <v>882.962</v>
+        <v>893.229</v>
       </c>
       <c r="G88">
         <v>69.8</v>
@@ -8497,28 +8497,28 @@
         <v>213.031</v>
       </c>
       <c r="M88">
-        <v>51.0352036</v>
+        <v>51.62863620000001</v>
       </c>
       <c r="N88">
-        <v>161.9957964</v>
+        <v>161.4023638</v>
       </c>
       <c r="O88">
-        <v>24.29936946</v>
+        <v>24.21035457</v>
       </c>
       <c r="P88">
-        <v>137.69642694</v>
+        <v>137.19200923</v>
       </c>
       <c r="Q88">
-        <v>138.16542694</v>
+        <v>137.66100923</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4906301073594648</v>
+        <v>0.524022811700677</v>
       </c>
       <c r="T88">
-        <v>6.123253864071946</v>
+        <v>6.582917008509035</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.174197122238972</v>
+        <v>4.126217844971857</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.110866065521088</v>
+        <v>0.1107921160118509</v>
       </c>
       <c r="C89">
-        <v>196.3748612276224</v>
+        <v>186.8053479897212</v>
       </c>
       <c r="D89">
-        <v>1019.803861227623</v>
+        <v>1020.501347989721</v>
       </c>
       <c r="E89">
-        <v>815.629</v>
+        <v>825.8960000000001</v>
       </c>
       <c r="F89">
-        <v>893.229</v>
+        <v>903.4960000000001</v>
       </c>
       <c r="G89">
         <v>69.8</v>
@@ -8579,28 +8579,28 @@
         <v>213.031</v>
       </c>
       <c r="M89">
-        <v>51.62863620000001</v>
+        <v>52.22206880000001</v>
       </c>
       <c r="N89">
-        <v>161.4023638</v>
+        <v>160.8089312</v>
       </c>
       <c r="O89">
-        <v>24.21035457</v>
+        <v>24.12133968</v>
       </c>
       <c r="P89">
-        <v>137.19200923</v>
+        <v>136.68759152</v>
       </c>
       <c r="Q89">
-        <v>137.66100923</v>
+        <v>137.15659152</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.524022811700677</v>
+        <v>0.5629809667654245</v>
       </c>
       <c r="T89">
-        <v>6.582917008509035</v>
+        <v>7.119190677018973</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.126217844971857</v>
+        <v>4.079329005824449</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1107921160118509</v>
+        <v>0.1107181665026139</v>
       </c>
       <c r="C90">
-        <v>186.8053479897212</v>
+        <v>177.2367894858797</v>
       </c>
       <c r="D90">
-        <v>1020.501347989721</v>
+        <v>1021.19978948588</v>
       </c>
       <c r="E90">
-        <v>825.8960000000001</v>
+        <v>836.163</v>
       </c>
       <c r="F90">
-        <v>903.4960000000001</v>
+        <v>913.763</v>
       </c>
       <c r="G90">
         <v>69.8</v>
@@ -8661,28 +8661,28 @@
         <v>213.031</v>
       </c>
       <c r="M90">
-        <v>52.22206880000001</v>
+        <v>52.8155014</v>
       </c>
       <c r="N90">
-        <v>160.8089312</v>
+        <v>160.2154986</v>
       </c>
       <c r="O90">
-        <v>24.12133968</v>
+        <v>24.03232479</v>
       </c>
       <c r="P90">
-        <v>136.68759152</v>
+        <v>136.18317381</v>
       </c>
       <c r="Q90">
-        <v>137.15659152</v>
+        <v>136.65217381</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5629809667654245</v>
+        <v>0.6090224227510352</v>
       </c>
       <c r="T90">
-        <v>7.119190677018973</v>
+        <v>7.752968648894353</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.079329005824449</v>
+        <v>4.033493848455635</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1107181665026139</v>
+        <v>0.1133217169933768</v>
       </c>
       <c r="C91">
-        <v>177.2367894858797</v>
+        <v>142.941815428455</v>
       </c>
       <c r="D91">
-        <v>1021.19978948588</v>
+        <v>997.171815428455</v>
       </c>
       <c r="E91">
-        <v>836.163</v>
+        <v>846.4300000000001</v>
       </c>
       <c r="F91">
-        <v>913.763</v>
+        <v>924.0300000000001</v>
       </c>
       <c r="G91">
         <v>69.8</v>
@@ -8743,45 +8743,45 @@
         <v>213.031</v>
       </c>
       <c r="M91">
-        <v>52.8155014</v>
+        <v>56.64303900000001</v>
       </c>
       <c r="N91">
-        <v>160.2154986</v>
+        <v>156.387961</v>
       </c>
       <c r="O91">
-        <v>24.03232479</v>
+        <v>23.45819415</v>
       </c>
       <c r="P91">
-        <v>136.18317381</v>
+        <v>132.92976685</v>
       </c>
       <c r="Q91">
-        <v>136.65217381</v>
+        <v>133.39876685</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6090224227510352</v>
+        <v>0.6642721699337681</v>
       </c>
       <c r="T91">
-        <v>7.752968648894353</v>
+        <v>8.513502215144811</v>
       </c>
       <c r="U91">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V91">
         <v>0.15</v>
       </c>
       <c r="W91">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.033493848455635</v>
+        <v>3.760938744829704</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1133217169933768</v>
+        <v>0.1132775174841397</v>
       </c>
       <c r="C92">
-        <v>142.941815428455</v>
+        <v>133.0732907110435</v>
       </c>
       <c r="D92">
-        <v>997.171815428455</v>
+        <v>997.5702907110435</v>
       </c>
       <c r="E92">
-        <v>846.4300000000001</v>
+        <v>856.697</v>
       </c>
       <c r="F92">
-        <v>924.0300000000001</v>
+        <v>934.297</v>
       </c>
       <c r="G92">
         <v>69.8</v>
@@ -8825,28 +8825,28 @@
         <v>213.031</v>
       </c>
       <c r="M92">
-        <v>56.64303900000001</v>
+        <v>57.2724061</v>
       </c>
       <c r="N92">
-        <v>156.387961</v>
+        <v>155.7585939</v>
       </c>
       <c r="O92">
-        <v>23.45819415</v>
+        <v>23.363789085</v>
       </c>
       <c r="P92">
-        <v>132.92976685</v>
+        <v>132.394804815</v>
       </c>
       <c r="Q92">
-        <v>133.39876685</v>
+        <v>132.863804815</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6642721699337681</v>
+        <v>0.7317996387126638</v>
       </c>
       <c r="T92">
-        <v>8.513502215144811</v>
+        <v>9.443043240562035</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.760938744829704</v>
+        <v>3.719609747633773</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1132775174841397</v>
+        <v>0.1132333179749027</v>
       </c>
       <c r="C93">
-        <v>133.0732907110435</v>
+        <v>123.2050845867254</v>
       </c>
       <c r="D93">
-        <v>997.5702907110435</v>
+        <v>997.9690845867256</v>
       </c>
       <c r="E93">
-        <v>856.697</v>
+        <v>866.9640000000001</v>
       </c>
       <c r="F93">
-        <v>934.297</v>
+        <v>944.5640000000001</v>
       </c>
       <c r="G93">
         <v>69.8</v>
@@ -8907,28 +8907,28 @@
         <v>213.031</v>
       </c>
       <c r="M93">
-        <v>57.2724061</v>
+        <v>57.90177320000001</v>
       </c>
       <c r="N93">
-        <v>155.7585939</v>
+        <v>155.1292268</v>
       </c>
       <c r="O93">
-        <v>23.363789085</v>
+        <v>23.26938402</v>
       </c>
       <c r="P93">
-        <v>132.394804815</v>
+        <v>131.85984278</v>
       </c>
       <c r="Q93">
-        <v>132.863804815</v>
+        <v>132.32884278</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7317996387126638</v>
+        <v>0.8162089746862836</v>
       </c>
       <c r="T93">
-        <v>9.443043240562035</v>
+        <v>10.60496952233357</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.719609747633773</v>
+        <v>3.679179206898624</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1132333179749027</v>
+        <v>0.1131891184656656</v>
       </c>
       <c r="C94">
-        <v>123.2050845867254</v>
+        <v>113.3371974377405</v>
       </c>
       <c r="D94">
-        <v>997.9690845867256</v>
+        <v>998.3681974377407</v>
       </c>
       <c r="E94">
-        <v>866.9640000000001</v>
+        <v>877.2310000000001</v>
       </c>
       <c r="F94">
-        <v>944.5640000000001</v>
+        <v>954.8310000000001</v>
       </c>
       <c r="G94">
         <v>69.8</v>
@@ -8989,28 +8989,28 @@
         <v>213.031</v>
       </c>
       <c r="M94">
-        <v>57.90177320000001</v>
+        <v>58.53114030000001</v>
       </c>
       <c r="N94">
-        <v>155.1292268</v>
+        <v>154.4998597</v>
       </c>
       <c r="O94">
-        <v>23.26938402</v>
+        <v>23.174978955</v>
       </c>
       <c r="P94">
-        <v>131.85984278</v>
+        <v>131.324880745</v>
       </c>
       <c r="Q94">
-        <v>132.32884278</v>
+        <v>131.793880745</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8162089746862836</v>
+        <v>0.9247352637952233</v>
       </c>
       <c r="T94">
-        <v>10.60496952233357</v>
+        <v>12.09887474175411</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.679179206898624</v>
+        <v>3.639618140157778</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1131891184656656</v>
+        <v>0.1131449189564285</v>
       </c>
       <c r="C95">
-        <v>113.3371974377405</v>
+        <v>103.4696296469411</v>
       </c>
       <c r="D95">
-        <v>998.3681974377407</v>
+        <v>998.7676296469411</v>
       </c>
       <c r="E95">
-        <v>877.2310000000001</v>
+        <v>887.498</v>
       </c>
       <c r="F95">
-        <v>954.8310000000001</v>
+        <v>965.0980000000001</v>
       </c>
       <c r="G95">
         <v>69.8</v>
@@ -9071,28 +9071,28 @@
         <v>213.031</v>
       </c>
       <c r="M95">
-        <v>58.53114030000001</v>
+        <v>59.16050740000001</v>
       </c>
       <c r="N95">
-        <v>154.4998597</v>
+        <v>153.8704926</v>
       </c>
       <c r="O95">
-        <v>23.174978955</v>
+        <v>23.08057389</v>
       </c>
       <c r="P95">
-        <v>131.324880745</v>
+        <v>130.78991871</v>
       </c>
       <c r="Q95">
-        <v>131.793880745</v>
+        <v>131.25891871</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9247352637952233</v>
+        <v>1.069436982607143</v>
       </c>
       <c r="T95">
-        <v>12.09887474175411</v>
+        <v>14.09074836764816</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.639618140157778</v>
+        <v>3.600898798241206</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1131449189564285</v>
+        <v>0.1131007194471914</v>
       </c>
       <c r="C96">
-        <v>103.4696296469411</v>
+        <v>93.60238159779135</v>
       </c>
       <c r="D96">
-        <v>998.7676296469411</v>
+        <v>999.1673815977914</v>
       </c>
       <c r="E96">
-        <v>887.498</v>
+        <v>897.7650000000001</v>
       </c>
       <c r="F96">
-        <v>965.0980000000001</v>
+        <v>975.3650000000001</v>
       </c>
       <c r="G96">
         <v>69.8</v>
@@ -9153,28 +9153,28 @@
         <v>213.031</v>
       </c>
       <c r="M96">
-        <v>59.16050740000001</v>
+        <v>59.78987450000001</v>
       </c>
       <c r="N96">
-        <v>153.8704926</v>
+        <v>153.2411255</v>
       </c>
       <c r="O96">
-        <v>23.08057389</v>
+        <v>22.986168825</v>
       </c>
       <c r="P96">
-        <v>130.78991871</v>
+        <v>130.254956675</v>
       </c>
       <c r="Q96">
-        <v>131.25891871</v>
+        <v>130.723956675</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.069436982607143</v>
+        <v>1.272019388943831</v>
       </c>
       <c r="T96">
-        <v>14.09074836764816</v>
+        <v>16.87937144389985</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.600898798241206</v>
+        <v>3.562994600364983</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1131007194471914</v>
+        <v>0.1130565199379544</v>
       </c>
       <c r="C97">
-        <v>93.60238159779135</v>
+        <v>83.73545367436975</v>
       </c>
       <c r="D97">
-        <v>999.1673815977914</v>
+        <v>999.56745367437</v>
       </c>
       <c r="E97">
-        <v>897.7650000000001</v>
+        <v>908.0320000000002</v>
       </c>
       <c r="F97">
-        <v>975.3650000000001</v>
+        <v>985.6320000000002</v>
       </c>
       <c r="G97">
         <v>69.8</v>
@@ -9235,28 +9235,28 @@
         <v>213.031</v>
       </c>
       <c r="M97">
-        <v>59.78987450000001</v>
+        <v>60.41924160000001</v>
       </c>
       <c r="N97">
-        <v>153.2411255</v>
+        <v>152.6117584</v>
       </c>
       <c r="O97">
-        <v>22.986168825</v>
+        <v>22.89176376</v>
       </c>
       <c r="P97">
-        <v>130.254956675</v>
+        <v>129.71999464</v>
       </c>
       <c r="Q97">
-        <v>130.723956675</v>
+        <v>130.18899464</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.272019388943831</v>
+        <v>1.575892998448863</v>
       </c>
       <c r="T97">
-        <v>16.87937144389985</v>
+        <v>21.06230605827737</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.562994600364983</v>
+        <v>3.525880073277847</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1130565199379544</v>
+        <v>0.1153209204287173</v>
       </c>
       <c r="C98">
-        <v>83.73545367437009</v>
+        <v>53.37617382902715</v>
       </c>
       <c r="D98">
-        <v>999.5674536743702</v>
+        <v>979.4751738290271</v>
       </c>
       <c r="E98">
-        <v>908.032</v>
+        <v>918.299</v>
       </c>
       <c r="F98">
-        <v>985.6320000000001</v>
+        <v>995.899</v>
       </c>
       <c r="G98">
         <v>69.8</v>
@@ -9317,45 +9317,45 @@
         <v>213.031</v>
       </c>
       <c r="M98">
-        <v>60.41924160000001</v>
+        <v>63.8371259</v>
       </c>
       <c r="N98">
-        <v>152.6117584</v>
+        <v>149.1938741</v>
       </c>
       <c r="O98">
-        <v>22.89176376</v>
+        <v>22.379081115</v>
       </c>
       <c r="P98">
-        <v>129.71999464</v>
+        <v>126.814792985</v>
       </c>
       <c r="Q98">
-        <v>130.18899464</v>
+        <v>127.283792985</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.575892998448858</v>
+        <v>2.082349014290575</v>
       </c>
       <c r="T98">
-        <v>21.06230605827731</v>
+        <v>28.03386374890648</v>
       </c>
       <c r="U98">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V98">
         <v>0.15</v>
       </c>
       <c r="W98">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.525880073277847</v>
+        <v>3.337101991930373</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1153209204287173</v>
+        <v>0.1153005209194802</v>
       </c>
       <c r="C99">
-        <v>53.37617382902715</v>
+        <v>43.28657467023174</v>
       </c>
       <c r="D99">
-        <v>979.4751738290271</v>
+        <v>979.6525746702317</v>
       </c>
       <c r="E99">
-        <v>918.299</v>
+        <v>928.566</v>
       </c>
       <c r="F99">
-        <v>995.899</v>
+        <v>1006.166</v>
       </c>
       <c r="G99">
         <v>69.8</v>
@@ -9399,28 +9399,28 @@
         <v>213.031</v>
       </c>
       <c r="M99">
-        <v>63.8371259</v>
+        <v>64.4952406</v>
       </c>
       <c r="N99">
-        <v>149.1938741</v>
+        <v>148.5357594</v>
       </c>
       <c r="O99">
-        <v>22.379081115</v>
+        <v>22.28036391</v>
       </c>
       <c r="P99">
-        <v>126.814792985</v>
+        <v>126.25539549</v>
       </c>
       <c r="Q99">
-        <v>127.283792985</v>
+        <v>126.72439549</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.082349014290575</v>
+        <v>3.095261045974009</v>
       </c>
       <c r="T99">
-        <v>28.03386374890648</v>
+        <v>41.97697913016483</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.337101991930373</v>
+        <v>3.303049930788227</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1153005209194802</v>
+        <v>0.1152801214102432</v>
       </c>
       <c r="C100">
-        <v>43.28657467023174</v>
+        <v>33.19703978414168</v>
       </c>
       <c r="D100">
-        <v>979.6525746702317</v>
+        <v>979.8300397841416</v>
       </c>
       <c r="E100">
-        <v>928.566</v>
+        <v>938.833</v>
       </c>
       <c r="F100">
-        <v>1006.166</v>
+        <v>1016.433</v>
       </c>
       <c r="G100">
         <v>69.8</v>
@@ -9481,28 +9481,28 @@
         <v>213.031</v>
       </c>
       <c r="M100">
-        <v>64.4952406</v>
+        <v>65.1533553</v>
       </c>
       <c r="N100">
-        <v>148.5357594</v>
+        <v>147.8776447</v>
       </c>
       <c r="O100">
-        <v>22.28036391</v>
+        <v>22.181646705</v>
       </c>
       <c r="P100">
-        <v>126.25539549</v>
+        <v>125.695997995</v>
       </c>
       <c r="Q100">
-        <v>126.72439549</v>
+        <v>126.164997995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.095261045974009</v>
+        <v>6.133997141024312</v>
       </c>
       <c r="T100">
-        <v>41.97697913016483</v>
+        <v>83.80632527393986</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.303049930788227</v>
+        <v>3.269685790073194</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1152801214102432</v>
-      </c>
-      <c r="C101">
-        <v>33.19703978414168</v>
-      </c>
-      <c r="D101">
-        <v>979.8300397841416</v>
-      </c>
-      <c r="E101">
-        <v>938.833</v>
-      </c>
-      <c r="F101">
-        <v>1016.433</v>
-      </c>
-      <c r="G101">
-        <v>69.8</v>
-      </c>
-      <c r="H101">
-        <v>949.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>213.5</v>
-      </c>
-      <c r="K101">
-        <v>0.469</v>
-      </c>
-      <c r="L101">
-        <v>213.031</v>
-      </c>
-      <c r="M101">
-        <v>65.1533553</v>
-      </c>
-      <c r="N101">
-        <v>147.8776447</v>
-      </c>
-      <c r="O101">
-        <v>22.181646705</v>
-      </c>
-      <c r="P101">
-        <v>125.695997995</v>
-      </c>
-      <c r="Q101">
-        <v>126.164997995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.133997141024312</v>
-      </c>
-      <c r="T101">
-        <v>83.80632527393986</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.054485</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.269685790073194</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
